--- a/All_ME_Oil_Gas_Jobs_Combined.xlsx
+++ b/All_ME_Oil_Gas_Jobs_Combined.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By Country" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Jobs'!$A$1:$G$747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Jobs'!$A$1:$G$756</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G747"/>
+  <dimension ref="A1:G756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19834,12 +19834,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>Gas Business Modeler</t>
+          <t>Industrial Communications Engineer</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>GO Technical Support &amp; Planning Dept</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -19849,12 +19849,12 @@
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17028</t>
+          <t>https://careers.aramco.com/expat_us/job/Industrial-Communications-Engineer/857079923/</t>
         </is>
       </c>
     </row>
@@ -19871,12 +19871,12 @@
       </c>
       <c r="C525" s="3" t="inlineStr">
         <is>
-          <t>Senior Writer/Editor</t>
+          <t>Sr Counsel - Corporate &amp; Project Finance</t>
         </is>
       </c>
       <c r="D525" s="3" t="inlineStr">
         <is>
-          <t>King Abdulaziz Center For World Culture</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E525" s="3" t="inlineStr">
@@ -19886,12 +19886,12 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16303</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel-Corporate-&amp;-Project-Finance/857034323/</t>
         </is>
       </c>
     </row>
@@ -19908,12 +19908,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>Gas Commercial Specialist</t>
+          <t>Tax Counsel</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>GO Technical Support &amp; Planning Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -19923,12 +19923,12 @@
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17029</t>
+          <t>https://careers.aramco.com/expat_uk/job/Tax-Counsel/857034223/</t>
         </is>
       </c>
     </row>
@@ -19945,12 +19945,12 @@
       </c>
       <c r="C527" s="3" t="inlineStr">
         <is>
-          <t>Lead Gas Master Planning Specialist</t>
+          <t>Infrastructure Facilities Planning Engineer</t>
         </is>
       </c>
       <c r="D527" s="3" t="inlineStr">
         <is>
-          <t>GO Technical Support &amp; Planning Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E527" s="3" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="F527" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17027</t>
+          <t>https://careers.aramco.com/expat_us/job/Infrastructure-Facilities-Planning-Engineer/857080223/</t>
         </is>
       </c>
     </row>
@@ -19982,12 +19982,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>Computing and IT Graduates (less than three years of work experience)</t>
+          <t>Substation Equipment Engineer</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -19997,12 +19997,12 @@
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/1408</t>
+          <t>https://careers.aramco.com/expat_us/job/Substation-Equipment-Engineer/857079523/</t>
         </is>
       </c>
     </row>
@@ -20019,12 +20019,12 @@
       </c>
       <c r="C529" s="3" t="inlineStr">
         <is>
-          <t>Business Graduates (less than three years of work experience)</t>
+          <t>Compressors &amp; Steam Turbines Engineer</t>
         </is>
       </c>
       <c r="D529" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E529" s="3" t="inlineStr">
@@ -20034,12 +20034,12 @@
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/1358</t>
+          <t>https://careers.aramco.com/expat_us/job/Compressors-&amp;-Steam-Turbines-Engineer/857079823/</t>
         </is>
       </c>
     </row>
@@ -20056,12 +20056,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>Safety Advisor</t>
+          <t>Heat Exchanger Engineer</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Group Safety Compliance Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -20071,12 +20071,12 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17228</t>
+          <t>https://careers.aramco.com/expat_us/job/Heat-Exchanger-Engineer/857079623/</t>
         </is>
       </c>
     </row>
@@ -20093,12 +20093,12 @@
       </c>
       <c r="C531" s="3" t="inlineStr">
         <is>
-          <t>Planning &amp; Performance Management Analyst</t>
+          <t>Sr Counsel - Joint Venture Development</t>
         </is>
       </c>
       <c r="D531" s="3" t="inlineStr">
         <is>
-          <t>Gas Plng &amp; Perf Mgmt Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E531" s="3" t="inlineStr">
@@ -20108,12 +20108,12 @@
       </c>
       <c r="F531" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16996</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel-Joint-Venture-Development/857034423/</t>
         </is>
       </c>
     </row>
@@ -20130,12 +20130,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>Engineering Graduates (less than three years of work experience)</t>
+          <t>Electrical Planning Engineer</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -20145,12 +20145,12 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/1344</t>
+          <t>https://careers.aramco.com/expat_us/job/Electrical-Planning-Engineer/857080323/</t>
         </is>
       </c>
     </row>
@@ -20167,12 +20167,12 @@
       </c>
       <c r="C533" s="3" t="inlineStr">
         <is>
-          <t>Reservoir Simulation Developer</t>
+          <t>Nonmetallic Engineering Specialist</t>
         </is>
       </c>
       <c r="D533" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E533" s="3" t="inlineStr">
@@ -20182,12 +20182,12 @@
       </c>
       <c r="F533" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16919</t>
+          <t>https://careers.aramco.com/expat_us/job/Nonmetallic-Engineering-Specialist/857079723/</t>
         </is>
       </c>
     </row>
@@ -20204,12 +20204,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>OSPAS Specialist</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Global Optimizer Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
@@ -20219,12 +20219,12 @@
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17506</t>
+          <t>https://careers.aramco.com/expat_us/job/Solution-Architect/857080123/</t>
         </is>
       </c>
     </row>
@@ -20241,12 +20241,12 @@
       </c>
       <c r="C535" s="3" t="inlineStr">
         <is>
-          <t>Lead Drilling Engineer</t>
+          <t>Sr Counsel - Venture Capital</t>
         </is>
       </c>
       <c r="D535" s="3" t="inlineStr">
         <is>
-          <t>Upstream JV Management</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E535" s="3" t="inlineStr">
@@ -20256,12 +20256,12 @@
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17248</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel-Venture-Capital/857034523/</t>
         </is>
       </c>
     </row>
@@ -20278,12 +20278,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>Well Intervention Specialist</t>
+          <t>Estimating Engineer</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>UR Completion Operations Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -20293,12 +20293,12 @@
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16653</t>
+          <t>https://careers.aramco.com/expat_us/job/Estimating-Engineer/857080423/</t>
         </is>
       </c>
     </row>
@@ -20315,12 +20315,12 @@
       </c>
       <c r="C537" s="3" t="inlineStr">
         <is>
-          <t>Accounting Analyst</t>
+          <t>Gas Business Modeler</t>
         </is>
       </c>
       <c r="D537" s="3" t="inlineStr">
         <is>
-          <t>Upstream Strategy &amp; Capital Plng Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E537" s="3" t="inlineStr">
@@ -20330,12 +20330,12 @@
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17000</t>
+          <t>https://careers.aramco.com/expat_us/job/Gas-Business-Modeler/857079023/</t>
         </is>
       </c>
     </row>
@@ -20352,12 +20352,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical Maintenance Engineer</t>
+          <t>Senior Writer/Editor</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>NA/SA Loss Prevention Dept</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -20367,12 +20367,12 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17274</t>
+          <t>https://careers.aramco.com/expat_us/job/Senior-WriterEditor/856486923/</t>
         </is>
       </c>
     </row>
@@ -20389,12 +20389,12 @@
       </c>
       <c r="C539" s="3" t="inlineStr">
         <is>
-          <t>Building Life Safety Plans Examiner</t>
+          <t>Gas Commercial Specialist</t>
         </is>
       </c>
       <c r="D539" s="3" t="inlineStr">
         <is>
-          <t>RT &amp; Regional Area Loss Prevention Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E539" s="3" t="inlineStr">
@@ -20404,12 +20404,12 @@
       </c>
       <c r="F539" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17224</t>
+          <t>https://careers.aramco.com/expat_uk/job/Gas-Commercial-Specialist/857079123/</t>
         </is>
       </c>
     </row>
@@ -20426,12 +20426,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>Safety Engineer (Drilling &amp; Workover Operations)</t>
+          <t>Lead Gas Master Planning Specialist</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>NA/SA Loss Prevention Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -20441,12 +20441,12 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17276</t>
+          <t>https://careers.aramco.com/expat_us/job/Lead-Gas-Master-Planning-Specialist/857078923/</t>
         </is>
       </c>
     </row>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="C541" s="3" t="inlineStr">
         <is>
-          <t>Business Writer</t>
+          <t>Computing and IT Graduates (less than three years of work experience)</t>
         </is>
       </c>
       <c r="D541" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E541" s="3" t="inlineStr">
@@ -20478,12 +20478,12 @@
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17394</t>
+          <t>https://careers.aramco.com/saudi/job/Computing-and-IT-Graduates-%28less-than-three-years-of-work-experience%29/766636523/</t>
         </is>
       </c>
     </row>
@@ -20500,12 +20500,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>D&amp;IT Affiliates Advisor</t>
+          <t>Business Graduates (less than three years of work experience)</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -20515,12 +20515,12 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G542" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17404</t>
+          <t>https://careers.aramco.com/saudi/job/Business-Graduates-%28less-than-three-years-of-work-experience%29/766636423/</t>
         </is>
       </c>
     </row>
@@ -20537,12 +20537,12 @@
       </c>
       <c r="C543" s="3" t="inlineStr">
         <is>
-          <t>Digital &amp; IT Strategy Consultant</t>
+          <t>Safety Advisor</t>
         </is>
       </c>
       <c r="D543" s="3" t="inlineStr">
         <is>
-          <t>D&amp;IT Strategy &amp; Investment Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E543" s="3" t="inlineStr">
@@ -20552,12 +20552,12 @@
       </c>
       <c r="F543" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17362</t>
+          <t>https://careers.aramco.com/expat_uk/job/Safety-Advisor/857078823/</t>
         </is>
       </c>
     </row>
@@ -20574,12 +20574,12 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>Business System Analyst</t>
+          <t>Planning &amp; Performance Management Analyst</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>DS Transformation &amp; Bus Excellence Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
@@ -20589,12 +20589,12 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17082</t>
+          <t>https://careers.aramco.com/expat_uk/job/Planning-&amp;-Performance-Management-Analyst/857100723/</t>
         </is>
       </c>
     </row>
@@ -20611,12 +20611,12 @@
       </c>
       <c r="C545" s="3" t="inlineStr">
         <is>
-          <t>Field Development Geologist</t>
+          <t>Engineering Graduates (less than three years of work experience)</t>
         </is>
       </c>
       <c r="D545" s="3" t="inlineStr">
         <is>
-          <t>Exploration Resource Assessment Dept</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E545" s="3" t="inlineStr">
@@ -20626,12 +20626,12 @@
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17199</t>
+          <t>https://careers.aramco.com/saudi/job/Engineering-Graduates-%28less-than-three-years-of-work-experience%29/766636323/</t>
         </is>
       </c>
     </row>
@@ -20648,12 +20648,12 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist</t>
+          <t>Reservoir Simulation Developer</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>DS Transformation &amp; Bus Excellence Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
@@ -20663,12 +20663,12 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17038</t>
+          <t>https://careers.aramco.com/expat_uk/job/Reservoir-Simulation-Developer/857078423/</t>
         </is>
       </c>
     </row>
@@ -20685,12 +20685,12 @@
       </c>
       <c r="C547" s="3" t="inlineStr">
         <is>
-          <t>Oil Reservoir Management Engineer</t>
+          <t>OSPAS Specialist</t>
         </is>
       </c>
       <c r="D547" s="3" t="inlineStr">
         <is>
-          <t>Safaniya Reservoir Mgmt Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E547" s="3" t="inlineStr">
@@ -20700,12 +20700,12 @@
       </c>
       <c r="F547" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16990</t>
+          <t>https://careers.aramco.com/expat_us/job/OSPAS-Specialist/857099923/</t>
         </is>
       </c>
     </row>
@@ -20722,12 +20722,12 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>Geomatics/Geographic Information Systems Analyst</t>
+          <t>Lead Drilling Engineer</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>Land Affairs Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
@@ -20737,12 +20737,12 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G548" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17434</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Drilling-Engineer/857100423/</t>
         </is>
       </c>
     </row>
@@ -20759,12 +20759,12 @@
       </c>
       <c r="C549" s="3" t="inlineStr">
         <is>
-          <t>Risk &amp; Resource Geoscientist</t>
+          <t>Accounting Analyst</t>
         </is>
       </c>
       <c r="D549" s="3" t="inlineStr">
         <is>
-          <t>UR Exploration &amp; Characterization Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E549" s="3" t="inlineStr">
@@ -20774,12 +20774,12 @@
       </c>
       <c r="F549" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16649</t>
+          <t>https://careers.aramco.com/expat_uk/job/Accounting-Analyst/857100023/</t>
         </is>
       </c>
     </row>
@@ -20796,12 +20796,12 @@
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>Facilities Engineer</t>
+          <t>Senior Mechanical Maintenance Engineer</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>Upstream Digital &amp; Computing Strtg Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
@@ -20811,12 +20811,12 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G550" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16924</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Mechanical-Maintenance-Engineer/857128623/</t>
         </is>
       </c>
     </row>
@@ -20833,12 +20833,12 @@
       </c>
       <c r="C551" s="3" t="inlineStr">
         <is>
-          <t>Environmental Coordinator</t>
+          <t>Lead Process Operations Engineer</t>
         </is>
       </c>
       <c r="D551" s="3" t="inlineStr">
         <is>
-          <t>Northern Area Onshore D&amp;WO Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E551" s="3" t="inlineStr">
@@ -20848,12 +20848,12 @@
       </c>
       <c r="F551" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17272</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Process-Operations-Engineer/857128423/</t>
         </is>
       </c>
     </row>
@@ -20870,12 +20870,12 @@
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>LNG Economist</t>
+          <t>Senior Contract Advisor</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>Gas Ventures Dept</t>
+          <t>Contracts &amp; Procurement</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr">
@@ -20885,12 +20885,12 @@
       </c>
       <c r="F552" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G552" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17067</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Contract-Advisor/857128523/</t>
         </is>
       </c>
     </row>
@@ -20907,12 +20907,12 @@
       </c>
       <c r="C553" s="3" t="inlineStr">
         <is>
-          <t>Deal Quality Specialist</t>
+          <t>Field Compliance Coordinator</t>
         </is>
       </c>
       <c r="D553" s="3" t="inlineStr">
         <is>
-          <t>Gas Ventures Dept</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E553" s="3" t="inlineStr">
@@ -20922,12 +20922,12 @@
       </c>
       <c r="F553" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17066</t>
+          <t>https://careers.aramco.com/expat_uk/job/Field-Compliance-Coordinator/857031723/</t>
         </is>
       </c>
     </row>
@@ -20944,12 +20944,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>LNG Sales &amp; Marketing Specialist</t>
+          <t>Security Investigator</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>Gas Ventures Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
@@ -20959,12 +20959,12 @@
       </c>
       <c r="F554" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G554" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17068</t>
+          <t>https://careers.aramco.com/expat_uk/job/Security-Investigator/857077823/</t>
         </is>
       </c>
     </row>
@@ -20981,12 +20981,12 @@
       </c>
       <c r="C555" s="3" t="inlineStr">
         <is>
-          <t>Subsurface Data Management Specialist</t>
+          <t>Information System Consultant</t>
         </is>
       </c>
       <c r="D555" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E555" s="3" t="inlineStr">
@@ -20996,12 +20996,12 @@
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17032</t>
+          <t>https://careers.aramco.com/expat_uk/job/Information-System-Consultant/857077223/</t>
         </is>
       </c>
     </row>
@@ -21018,12 +21018,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>Industrial Computer Engineer</t>
+          <t>Safety Engineer</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>Marine Techl Support Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
@@ -21033,12 +21033,12 @@
       </c>
       <c r="F556" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17326</t>
+          <t>https://careers.aramco.com/expat_uk/job/Safety-Engineer/857078223/</t>
         </is>
       </c>
     </row>
@@ -21055,12 +21055,12 @@
       </c>
       <c r="C557" s="3" t="inlineStr">
         <is>
-          <t>Senior Diving Inspection Specialist</t>
+          <t>Fire Protection Engineer</t>
         </is>
       </c>
       <c r="D557" s="3" t="inlineStr">
         <is>
-          <t>RT &amp; WR Marine Ops Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E557" s="3" t="inlineStr">
@@ -21070,12 +21070,12 @@
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17338</t>
+          <t>https://careers.aramco.com/expat_uk/job/Fire-Protection-Engineer/857077623/</t>
         </is>
       </c>
     </row>
@@ -21092,12 +21092,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>Diving Specialist</t>
+          <t>Process Safety Engineer</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>RT &amp; WR Marine Ops Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -21107,12 +21107,12 @@
       </c>
       <c r="F558" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17340</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Safety-Engineer/857078123/</t>
         </is>
       </c>
     </row>
@@ -21129,12 +21129,12 @@
       </c>
       <c r="C559" s="3" t="inlineStr">
         <is>
-          <t>International Media Relations Specialist</t>
+          <t>Well Intervention Specialist</t>
         </is>
       </c>
       <c r="D559" s="3" t="inlineStr">
         <is>
-          <t>Media Communications &amp; Coordination Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E559" s="3" t="inlineStr">
@@ -21144,12 +21144,12 @@
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17602</t>
+          <t>https://careers.aramco.com/expat_us/job/Well-Intervention-Specialist/857031223/</t>
         </is>
       </c>
     </row>
@@ -21166,12 +21166,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>Program Manager and Development Advisor</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>Mgmt &amp; Professional Development Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -21181,12 +21181,12 @@
       </c>
       <c r="F560" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17261</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Engineer/857077023/</t>
         </is>
       </c>
     </row>
@@ -21203,12 +21203,12 @@
       </c>
       <c r="C561" s="3" t="inlineStr">
         <is>
-          <t>Credit Risk Management Analyst</t>
+          <t>Building Life Safety Plans Examiner</t>
         </is>
       </c>
       <c r="D561" s="3" t="inlineStr">
         <is>
-          <t>Financial Risk Management Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E561" s="3" t="inlineStr">
@@ -21218,12 +21218,12 @@
       </c>
       <c r="F561" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16894</t>
+          <t>https://careers.aramco.com/expat_uk/job/Building-Life-Safety-Plans-Examiner/857078023/</t>
         </is>
       </c>
     </row>
@@ -21240,12 +21240,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>Lead Financial Analyst</t>
+          <t>Safety Engineer (Drilling &amp; Workover Operations)</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>Policy &amp; Corporate Finance Strategy Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
@@ -21255,12 +21255,12 @@
       </c>
       <c r="F562" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16928</t>
+          <t>https://careers.aramco.com/expat_uk/job/Safety-Engineer-%28Drilling-&amp;-Workover-Operations%29/857078323/</t>
         </is>
       </c>
     </row>
@@ -21277,12 +21277,12 @@
       </c>
       <c r="C563" s="3" t="inlineStr">
         <is>
-          <t>Assessment &amp; Coaching Subject Matter Expert</t>
+          <t>Business Writer</t>
         </is>
       </c>
       <c r="D563" s="3" t="inlineStr">
         <is>
-          <t>Mgmt &amp; Professional Development Dept</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr">
@@ -21292,12 +21292,12 @@
       </c>
       <c r="F563" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17260</t>
+          <t>https://careers.aramco.com/expat_us/job/Business-Writer/857077323/</t>
         </is>
       </c>
     </row>
@@ -21314,12 +21314,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>Career Development Specialist</t>
+          <t>D&amp;IT Affiliates Advisor</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>Mgmt &amp; Professional Development Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -21329,12 +21329,12 @@
       </c>
       <c r="F564" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17262</t>
+          <t>https://careers.aramco.com/expat_uk/job/D&amp;IT-Affiliates-Advisor/857077123/</t>
         </is>
       </c>
     </row>
@@ -21351,12 +21351,12 @@
       </c>
       <c r="C565" s="3" t="inlineStr">
         <is>
-          <t>Management and Professional Trainer</t>
+          <t>Digital &amp; IT Strategy Consultant</t>
         </is>
       </c>
       <c r="D565" s="3" t="inlineStr">
         <is>
-          <t>Mgmt &amp; Professional Development Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E565" s="3" t="inlineStr">
@@ -21366,12 +21366,12 @@
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17263</t>
+          <t>https://careers.aramco.com/expat_uk/job/Digital-&amp;-IT-Strategy-Consultant/857076323/</t>
         </is>
       </c>
     </row>
@@ -21388,12 +21388,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>Senior Accounting Analyst</t>
+          <t>Business System Analyst</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>Medical Services &amp; Affiliates Mgmt Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
@@ -21403,12 +21403,12 @@
       </c>
       <c r="F566" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17540</t>
+          <t>https://careers.aramco.com/expat_uk/job/Business-System-Analyst/857099523/</t>
         </is>
       </c>
     </row>
@@ -21425,12 +21425,12 @@
       </c>
       <c r="C567" s="3" t="inlineStr">
         <is>
-          <t>Gas Reservoir Engineer</t>
+          <t>Field Development Geologist</t>
         </is>
       </c>
       <c r="D567" s="3" t="inlineStr">
         <is>
-          <t>Gas Strategy &amp; Technical Support Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E567" s="3" t="inlineStr">
@@ -21440,12 +21440,12 @@
       </c>
       <c r="F567" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17684</t>
+          <t>https://careers.aramco.com/expat_uk/job/Field-Development-Geologist/857076523/</t>
         </is>
       </c>
     </row>
@@ -21462,12 +21462,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>Linear Programming (LP) Modeling Engineer</t>
+          <t>Data Scientist Specialist</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>OSPAS Planning &amp; Technical Support Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr">
@@ -21477,12 +21477,12 @@
       </c>
       <c r="F568" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17091</t>
+          <t>https://careers.aramco.com/expat_uk/job/Data-Scientist-Specialist/857099623/</t>
         </is>
       </c>
     </row>
@@ -21499,12 +21499,12 @@
       </c>
       <c r="C569" s="3" t="inlineStr">
         <is>
-          <t>Project Support Engineer</t>
+          <t>Oil Reservoir Management Engineer</t>
         </is>
       </c>
       <c r="D569" s="3" t="inlineStr">
         <is>
-          <t>NA/SA Loss Prevention Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E569" s="3" t="inlineStr">
@@ -21514,12 +21514,12 @@
       </c>
       <c r="F569" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17275</t>
+          <t>https://careers.aramco.com/expat_uk/job/Oil-Reservoir-Management-Engineer/857030523/</t>
         </is>
       </c>
     </row>
@@ -21536,12 +21536,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>AFFILIATES MANAGEMENT ADVISOR</t>
+          <t>Geomatics/Geographic Information Systems Analyst</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>Eastern Region Fuels Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -21551,12 +21551,12 @@
       </c>
       <c r="F570" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17084</t>
+          <t>https://careers.aramco.com/expat_uk/job/GeomaticsGeographic-Information-Systems-Analyst/857076723/</t>
         </is>
       </c>
     </row>
@@ -21573,12 +21573,12 @@
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>Affiliate Financial Advisor</t>
+          <t>Risk &amp; Resource Geoscientist</t>
         </is>
       </c>
       <c r="D571" s="3" t="inlineStr">
         <is>
-          <t>Western Region Fuels Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E571" s="3" t="inlineStr">
@@ -21588,12 +21588,12 @@
       </c>
       <c r="F571" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17083</t>
+          <t>https://careers.aramco.com/expat_uk/job/Risk-&amp;-Resource-Geoscientist/856937223/</t>
         </is>
       </c>
     </row>
@@ -21610,12 +21610,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>English Content Creator</t>
+          <t>Facilities Engineer</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>Communication Content &amp; Channels Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -21625,12 +21625,12 @@
       </c>
       <c r="F572" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17479</t>
+          <t>https://careers.aramco.com/expat_us/job/Facilities-Engineer/857074923/</t>
         </is>
       </c>
     </row>
@@ -21647,12 +21647,12 @@
       </c>
       <c r="C573" s="3" t="inlineStr">
         <is>
-          <t>Litigation Counsel</t>
+          <t>Environmental Coordinator</t>
         </is>
       </c>
       <c r="D573" s="3" t="inlineStr">
         <is>
-          <t>International Litigation &amp; ADR Dept</t>
+          <t>Environmental &amp; Sustainability</t>
         </is>
       </c>
       <c r="E573" s="3" t="inlineStr">
@@ -21662,12 +21662,12 @@
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16818</t>
+          <t>https://careers.aramco.com/expat_uk/job/Environmental-Coordinator/857098323/</t>
         </is>
       </c>
     </row>
@@ -21684,12 +21684,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>Downstream Transformation Analyst</t>
+          <t>LNG Economist</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>DS Transformation &amp; Bus Excellence Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -21699,12 +21699,12 @@
       </c>
       <c r="F574" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17037</t>
+          <t>https://careers.aramco.com/expat_us/job/LNG-Economist/857075823/</t>
         </is>
       </c>
     </row>
@@ -21721,12 +21721,12 @@
       </c>
       <c r="C575" s="3" t="inlineStr">
         <is>
-          <t>Digital Marketing Analyst</t>
+          <t>Deal Quality Specialist</t>
         </is>
       </c>
       <c r="D575" s="3" t="inlineStr">
         <is>
-          <t>Communication Content &amp; Channels Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E575" s="3" t="inlineStr">
@@ -21736,12 +21736,12 @@
       </c>
       <c r="F575" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16307</t>
+          <t>https://careers.aramco.com/expat_us/job/Deal-Quality-Specialist/857075723/</t>
         </is>
       </c>
     </row>
@@ -21758,12 +21758,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>Capital Markets Financial Analyst</t>
+          <t>LNG Sales &amp; Marketing Specialist</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>Capital Markets &amp; Financing Dept</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -21773,12 +21773,12 @@
       </c>
       <c r="F576" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16895</t>
+          <t>https://careers.aramco.com/expat_us/job/LNG-Sales-&amp;-Marketing-Specialist/857075923/</t>
         </is>
       </c>
     </row>
@@ -21795,12 +21795,12 @@
       </c>
       <c r="C577" s="3" t="inlineStr">
         <is>
-          <t>Strategy &amp; Energy Market Specialist</t>
+          <t>Subsurface Data Management Specialist</t>
         </is>
       </c>
       <c r="D577" s="3" t="inlineStr">
         <is>
-          <t>Policy &amp; Corporate Finance Strategy Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E577" s="3" t="inlineStr">
@@ -21810,12 +21810,12 @@
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G577" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16917</t>
+          <t>https://careers.aramco.com/expat_us/job/Subsurface-Data-Management-Specialist/857075623/</t>
         </is>
       </c>
     </row>
@@ -21832,12 +21832,12 @@
       </c>
       <c r="C578" s="2" t="inlineStr">
         <is>
-          <t>Insurance Risk Specialist</t>
+          <t>Industrial Computer Engineer</t>
         </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>Financial Risk Management Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr">
@@ -21847,12 +21847,12 @@
       </c>
       <c r="F578" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16893</t>
+          <t>https://careers.aramco.com/expat_uk/job/Industrial-Computer-Engineer/857075023/</t>
         </is>
       </c>
     </row>
@@ -21869,12 +21869,12 @@
       </c>
       <c r="C579" s="3" t="inlineStr">
         <is>
-          <t>Senior Archivist</t>
+          <t>Senior Diving Inspection Specialist</t>
         </is>
       </c>
       <c r="D579" s="3" t="inlineStr">
         <is>
-          <t>Communication Content &amp; Channels Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E579" s="3" t="inlineStr">
@@ -21884,12 +21884,12 @@
       </c>
       <c r="F579" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16310</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Diving-Inspection-Specialist/857075123/</t>
         </is>
       </c>
     </row>
@@ -21906,12 +21906,12 @@
       </c>
       <c r="C580" s="2" t="inlineStr">
         <is>
-          <t>Oil Reservoir Management Engineer</t>
+          <t>Diving Specialist</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>NA Reservoir Management Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E580" s="2" t="inlineStr">
@@ -21921,12 +21921,12 @@
       </c>
       <c r="F580" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16920</t>
+          <t>https://careers.aramco.com/expat_uk/job/Diving-Specialist/857075223/</t>
         </is>
       </c>
     </row>
@@ -21943,12 +21943,12 @@
       </c>
       <c r="C581" s="3" t="inlineStr">
         <is>
-          <t>Project Finance Specialist</t>
+          <t>International Media Relations Specialist</t>
         </is>
       </c>
       <c r="D581" s="3" t="inlineStr">
         <is>
-          <t>Capital Markets &amp; Financing Dept</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E581" s="3" t="inlineStr">
@@ -21958,12 +21958,12 @@
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16892</t>
+          <t>https://careers.aramco.com/expat_uk/job/International-Media-Relations-Specialist/857098723/</t>
         </is>
       </c>
     </row>
@@ -21980,12 +21980,12 @@
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>Venture Building Expert</t>
+          <t>Program Manager and Development Advisor</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
@@ -21995,12 +21995,12 @@
       </c>
       <c r="F582" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16995</t>
+          <t>https://careers.aramco.com/expat_us/job/Program-Manager-and-Development-Advisor/857074023/</t>
         </is>
       </c>
     </row>
@@ -22017,12 +22017,12 @@
       </c>
       <c r="C583" s="3" t="inlineStr">
         <is>
-          <t>Treasury Analyst</t>
+          <t>Credit Risk Management Analyst</t>
         </is>
       </c>
       <c r="D583" s="3" t="inlineStr">
         <is>
-          <t>Group Treasury Mgmt Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E583" s="3" t="inlineStr">
@@ -22032,12 +22032,12 @@
       </c>
       <c r="F583" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G583" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16915</t>
+          <t>https://careers.aramco.com/expat_uk/job/Credit-Risk-Management-Analyst/857028523/</t>
         </is>
       </c>
     </row>
@@ -22054,12 +22054,12 @@
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>Affiliate Finance Advisor</t>
+          <t>Lead Financial Analyst</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
@@ -22069,12 +22069,12 @@
       </c>
       <c r="F584" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17092</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Financial-Analyst/857073823/</t>
         </is>
       </c>
     </row>
@@ -22091,12 +22091,12 @@
       </c>
       <c r="C585" s="3" t="inlineStr">
         <is>
-          <t>Cash Management Treasury Analyst</t>
+          <t>Assessment &amp; Coaching Subject Matter Expert</t>
         </is>
       </c>
       <c r="D585" s="3" t="inlineStr">
         <is>
-          <t>Group Treasury Mgmt Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E585" s="3" t="inlineStr">
@@ -22106,12 +22106,12 @@
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G585" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16913</t>
+          <t>https://careers.aramco.com/expat_us/job/Assessment-&amp;-Coaching-Subject-Matter-Expert/857074123/</t>
         </is>
       </c>
     </row>
@@ -22128,12 +22128,12 @@
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>Debt Management Specialist</t>
+          <t>Career Development Specialist</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>Group Treasury Mgmt Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
@@ -22143,12 +22143,12 @@
       </c>
       <c r="F586" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16927</t>
+          <t>https://careers.aramco.com/expat_us/job/Career-Development-Specialist/857074223/</t>
         </is>
       </c>
     </row>
@@ -22165,12 +22165,12 @@
       </c>
       <c r="C587" s="3" t="inlineStr">
         <is>
-          <t>Crisis and Business Continuity Advisor</t>
+          <t>Management and Professional Trainer</t>
         </is>
       </c>
       <c r="D587" s="3" t="inlineStr">
         <is>
-          <t>OSPAS Planning &amp; Technical Support Dept</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E587" s="3" t="inlineStr">
@@ -22180,12 +22180,12 @@
       </c>
       <c r="F587" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G587" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17090</t>
+          <t>https://careers.aramco.com/expat_us/job/Management-and-Professional-Trainer/857074323/</t>
         </is>
       </c>
     </row>
@@ -22202,12 +22202,12 @@
       </c>
       <c r="C588" s="2" t="inlineStr">
         <is>
-          <t>Safety Engineer - Marine Operations</t>
+          <t>Senior Accounting Analyst</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>RT &amp; Regional Area Loss Prevention Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
@@ -22217,12 +22217,12 @@
       </c>
       <c r="F588" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17223</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Accounting-Analyst/857097423/</t>
         </is>
       </c>
     </row>
@@ -22239,12 +22239,12 @@
       </c>
       <c r="C589" s="3" t="inlineStr">
         <is>
-          <t>Safety Engineer - Aviation Operations</t>
+          <t>Gas Reservoir Engineer</t>
         </is>
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>LP Technical Services Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E589" s="3" t="inlineStr">
@@ -22254,12 +22254,12 @@
       </c>
       <c r="F589" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G589" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17218</t>
+          <t>https://careers.aramco.com/expat_uk/job/Gas-Reservoir-Engineer/857121923/</t>
         </is>
       </c>
     </row>
@@ -22276,12 +22276,12 @@
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>Petroleum Engineer Systems Analyst</t>
+          <t>Linear Programming (LP) Modeling Engineer</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>Drilling Technical Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="F590" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17258</t>
+          <t>https://careers.aramco.com/expat_uk/job/Linear-Programming-%28LP%29-Modeling-Engineer/857096723/</t>
         </is>
       </c>
     </row>
@@ -22313,12 +22313,12 @@
       </c>
       <c r="C591" s="3" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Project Support Engineer</t>
         </is>
       </c>
       <c r="D591" s="3" t="inlineStr">
         <is>
-          <t>Special Projects</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E591" s="3" t="inlineStr">
@@ -22328,12 +22328,12 @@
       </c>
       <c r="F591" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G591" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16348</t>
+          <t>https://careers.aramco.com/expat_uk/job/Project-Support-Engineer/857121123/</t>
         </is>
       </c>
     </row>
@@ -22350,12 +22350,12 @@
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>Sr Counsel - Manufacturing &amp; Power Practice</t>
+          <t>AFFILIATES MANAGEMENT ADVISOR</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>Global Manufacturing Law Dept</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
@@ -22365,12 +22365,12 @@
       </c>
       <c r="F592" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16176</t>
+          <t>https://careers.aramco.com/expat_us/job/AFFILIATES-MANAGEMENT-ADVISOR/857095723/</t>
         </is>
       </c>
     </row>
@@ -22387,12 +22387,12 @@
       </c>
       <c r="C593" s="3" t="inlineStr">
         <is>
-          <t>Drilling Engineer</t>
+          <t>Affiliate Financial Advisor</t>
         </is>
       </c>
       <c r="D593" s="3" t="inlineStr">
         <is>
-          <t>Gas Drilling Engrg Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E593" s="3" t="inlineStr">
@@ -22402,12 +22402,12 @@
       </c>
       <c r="F593" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G593" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17211</t>
+          <t>https://careers.aramco.com/expat_us/job/Affiliate-Financial-Advisor/857095623/</t>
         </is>
       </c>
     </row>
@@ -22424,12 +22424,12 @@
       </c>
       <c r="C594" s="2" t="inlineStr">
         <is>
-          <t>Upstream &amp; LNG Strategist</t>
+          <t>English Content Creator</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
@@ -22439,12 +22439,12 @@
       </c>
       <c r="F594" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G594" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17533</t>
+          <t>https://careers.aramco.com/expat_us/job/English-Content-Creator/857096123/</t>
         </is>
       </c>
     </row>
@@ -22461,12 +22461,12 @@
       </c>
       <c r="C595" s="3" t="inlineStr">
         <is>
-          <t>Process Engineer - Solomon Benchmarking - Refinery Experience Only</t>
+          <t>Litigation Counsel</t>
         </is>
       </c>
       <c r="D595" s="3" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E595" s="3" t="inlineStr">
@@ -22476,12 +22476,12 @@
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G595" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15346</t>
+          <t>https://careers.aramco.com/expat_uk/job/Litigation-Counsel/857120423/</t>
         </is>
       </c>
     </row>
@@ -22498,12 +22498,12 @@
       </c>
       <c r="C596" s="2" t="inlineStr">
         <is>
-          <t>Compliance Counsel</t>
+          <t>Downstream Transformation Analyst</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>Transactions,Sustain &amp; Rept'g Compl Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
@@ -22513,12 +22513,12 @@
       </c>
       <c r="F596" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16822</t>
+          <t>https://careers.aramco.com/expat_uk/job/Downstream-Transformation-Analyst/857120823/</t>
         </is>
       </c>
     </row>
@@ -22535,12 +22535,12 @@
       </c>
       <c r="C597" s="3" t="inlineStr">
         <is>
-          <t>Accounting Analyst</t>
+          <t>Digital Marketing Analyst</t>
         </is>
       </c>
       <c r="D597" s="3" t="inlineStr">
         <is>
-          <t>Group Finance &amp; Consulting Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E597" s="3" t="inlineStr">
@@ -22550,12 +22550,12 @@
       </c>
       <c r="F597" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G597" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17286</t>
+          <t>https://careers.aramco.com/expat_us/job/Digital-Marketing-Analyst/856442623/</t>
         </is>
       </c>
     </row>
@@ -22572,12 +22572,12 @@
       </c>
       <c r="C598" s="2" t="inlineStr">
         <is>
-          <t>Elementary-Intermediate Teacher</t>
+          <t>Capital Markets Financial Analyst</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
@@ -22587,12 +22587,12 @@
       </c>
       <c r="F598" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17282</t>
+          <t>https://careers.aramco.com/expat_uk/job/Capital-Markets-Financial-Analyst/857027123/</t>
         </is>
       </c>
     </row>
@@ -22609,12 +22609,12 @@
       </c>
       <c r="C599" s="3" t="inlineStr">
         <is>
-          <t>Lead Field Compliance Coordinator</t>
+          <t>Strategy &amp; Energy Market Specialist</t>
         </is>
       </c>
       <c r="D599" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E599" s="3" t="inlineStr">
@@ -22624,12 +22624,12 @@
       </c>
       <c r="F599" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G599" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16987</t>
+          <t>https://careers.aramco.com/expat_uk/job/Strategy-&amp;-Energy-Market-Specialist/857027423/</t>
         </is>
       </c>
     </row>
@@ -22646,12 +22646,12 @@
       </c>
       <c r="C600" s="2" t="inlineStr">
         <is>
-          <t>Business Development Specialist - Transaction &amp; Execution</t>
+          <t>Insurance Risk Specialist</t>
         </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>Core JV's Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="F600" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G600" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17519</t>
+          <t>https://careers.aramco.com/expat_uk/job/Insurance-Risk-Specialist/857027323/</t>
         </is>
       </c>
     </row>
@@ -22683,12 +22683,12 @@
       </c>
       <c r="C601" s="3" t="inlineStr">
         <is>
-          <t>AI Governance Officer</t>
+          <t>Senior Archivist</t>
         </is>
       </c>
       <c r="D601" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E601" s="3" t="inlineStr">
@@ -22698,12 +22698,12 @@
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G601" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16624</t>
+          <t>https://careers.aramco.com/expat_us/job/Senior-Archivist/856442923/</t>
         </is>
       </c>
     </row>
@@ -22720,12 +22720,12 @@
       </c>
       <c r="C602" s="2" t="inlineStr">
         <is>
-          <t>Speechwriter</t>
+          <t>Oil Reservoir Management Engineer</t>
         </is>
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>Executive Comms &amp; Alignment Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E602" s="2" t="inlineStr">
@@ -22735,12 +22735,12 @@
       </c>
       <c r="F602" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G602" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16345</t>
+          <t>https://careers.aramco.com/expat_uk/job/Oil-Reservoir-Management-Engineer/857023723/</t>
         </is>
       </c>
     </row>
@@ -22757,12 +22757,12 @@
       </c>
       <c r="C603" s="3" t="inlineStr">
         <is>
-          <t>Affiliates Management Advisor - Medical Services</t>
+          <t>Project Finance Specialist</t>
         </is>
       </c>
       <c r="D603" s="3" t="inlineStr">
         <is>
-          <t>Medical Services &amp; Affiliates Mgmt Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E603" s="3" t="inlineStr">
@@ -22772,12 +22772,12 @@
       </c>
       <c r="F603" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G603" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17494</t>
+          <t>https://careers.aramco.com/expat_uk/job/Project-Finance-Specialist/857027223/</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22794,7 @@
       </c>
       <c r="C604" s="2" t="inlineStr">
         <is>
-          <t>Mineral Strategy Analyst</t>
+          <t>Venture Building Expert</t>
         </is>
       </c>
       <c r="D604" s="2" t="inlineStr">
@@ -22809,12 +22809,12 @@
       </c>
       <c r="F604" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G604" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16882</t>
+          <t>https://careers.aramco.com/expat_uk/job/Venture-Building-Expert/857026123/</t>
         </is>
       </c>
     </row>
@@ -22831,12 +22831,12 @@
       </c>
       <c r="C605" s="3" t="inlineStr">
         <is>
-          <t>Onshore Structural Engineer</t>
+          <t>Treasury Analyst</t>
         </is>
       </c>
       <c r="D605" s="3" t="inlineStr">
         <is>
-          <t>Equipment Consulting Services Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E605" s="3" t="inlineStr">
@@ -22846,12 +22846,12 @@
       </c>
       <c r="F605" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G605" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17288</t>
+          <t>https://careers.aramco.com/expat_uk/job/Treasury-Analyst/857023123/</t>
         </is>
       </c>
     </row>
@@ -22868,12 +22868,12 @@
       </c>
       <c r="C606" s="2" t="inlineStr">
         <is>
-          <t>Business Development Specialist - Transaction Execution</t>
+          <t>Affiliate Finance Advisor</t>
         </is>
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>Divestments Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
@@ -22883,12 +22883,12 @@
       </c>
       <c r="F606" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G606" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17246</t>
+          <t>https://careers.aramco.com/expat_uk/job/Affiliate-Finance-Advisor/857068423/</t>
         </is>
       </c>
     </row>
@@ -22905,12 +22905,12 @@
       </c>
       <c r="C607" s="3" t="inlineStr">
         <is>
-          <t>Lead Accounting Analyst</t>
+          <t>Cash Management Treasury Analyst</t>
         </is>
       </c>
       <c r="D607" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E607" s="3" t="inlineStr">
@@ -22920,12 +22920,12 @@
       </c>
       <c r="F607" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G607" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16682</t>
+          <t>https://careers.aramco.com/expat_uk/job/Cash-Management-Treasury-Analyst/857023023/</t>
         </is>
       </c>
     </row>
@@ -22942,12 +22942,12 @@
       </c>
       <c r="C608" s="2" t="inlineStr">
         <is>
-          <t>Process Modeling Specialist</t>
+          <t>Debt Management Specialist</t>
         </is>
       </c>
       <c r="D608" s="2" t="inlineStr">
         <is>
-          <t>Process &amp; Control Systems Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E608" s="2" t="inlineStr">
@@ -22957,12 +22957,12 @@
       </c>
       <c r="F608" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G608" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17425</t>
+          <t>https://careers.aramco.com/expat_uk/job/Debt-Management-Specialist/857021523/</t>
         </is>
       </c>
     </row>
@@ -22979,12 +22979,12 @@
       </c>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>Gas &amp; NGL Planning Engineer</t>
+          <t>Crisis and Business Continuity Advisor</t>
         </is>
       </c>
       <c r="D609" s="3" t="inlineStr">
         <is>
-          <t>Process Facilities Planning Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E609" s="3" t="inlineStr">
@@ -22994,12 +22994,12 @@
       </c>
       <c r="F609" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17484</t>
+          <t>https://careers.aramco.com/expat_uk/job/Crisis-and-Business-Continuity-Advisor/857070923/</t>
         </is>
       </c>
     </row>
@@ -23016,12 +23016,12 @@
       </c>
       <c r="C610" s="2" t="inlineStr">
         <is>
-          <t>Process Simulation Twin &amp; Optimization Engineer - Refinery Experience Only</t>
+          <t>Safety Engineer - Marine Operations</t>
         </is>
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>Reliability Solutions Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
@@ -23031,12 +23031,12 @@
       </c>
       <c r="F610" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G610" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17346</t>
+          <t>https://careers.aramco.com/expat_uk/job/Safety-Engineer-Marine-Operations/857093823/</t>
         </is>
       </c>
     </row>
@@ -23053,12 +23053,12 @@
       </c>
       <c r="C611" s="3" t="inlineStr">
         <is>
-          <t>Sr Strategy &amp; Market Consultant</t>
+          <t>Safety Engineer - Aviation Operations</t>
         </is>
       </c>
       <c r="D611" s="3" t="inlineStr">
         <is>
-          <t>Downstream Strategy &amp; Capital Plng Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E611" s="3" t="inlineStr">
@@ -23068,12 +23068,12 @@
       </c>
       <c r="F611" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G611" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17412</t>
+          <t>https://careers.aramco.com/expat_uk/job/Safety-Engineer-Aviation-Operations/857093923/</t>
         </is>
       </c>
     </row>
@@ -23090,12 +23090,12 @@
       </c>
       <c r="C612" s="2" t="inlineStr">
         <is>
-          <t>Operational Excellence Specialist</t>
+          <t>Petroleum Engineer Systems Analyst</t>
         </is>
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>Operational Excellence Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E612" s="2" t="inlineStr">
@@ -23105,12 +23105,12 @@
       </c>
       <c r="F612" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G612" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17384</t>
+          <t>https://careers.aramco.com/expat_uk/job/Petroleum-Engineer-Systems-Analyst/857094823/</t>
         </is>
       </c>
     </row>
@@ -23127,12 +23127,12 @@
       </c>
       <c r="C613" s="3" t="inlineStr">
         <is>
-          <t>Instructional Designer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="D613" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E613" s="3" t="inlineStr">
@@ -23142,12 +23142,12 @@
       </c>
       <c r="F613" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G613" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16753</t>
+          <t>https://careers.aramco.com/expat_us/job/Architect/856539023/</t>
         </is>
       </c>
     </row>
@@ -23164,12 +23164,12 @@
       </c>
       <c r="C614" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Performance Expert - Refinery Experience Only</t>
+          <t>Sr Counsel - Manufacturing &amp; Power Practice</t>
         </is>
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>Tech &amp; Manufacturing Oversight Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E614" s="2" t="inlineStr">
@@ -23179,12 +23179,12 @@
       </c>
       <c r="F614" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G614" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15547</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel-Manufacturing-&amp;-Power-Practice/856316523/</t>
         </is>
       </c>
     </row>
@@ -23201,12 +23201,12 @@
       </c>
       <c r="C615" s="3" t="inlineStr">
         <is>
-          <t>Field Compliance Coordinator</t>
+          <t>Drilling Engineer</t>
         </is>
       </c>
       <c r="D615" s="3" t="inlineStr">
         <is>
-          <t>TS Business Support Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E615" s="3" t="inlineStr">
@@ -23216,12 +23216,12 @@
       </c>
       <c r="F615" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G615" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17317</t>
+          <t>https://careers.aramco.com/expat_uk/job/Drilling-Engineer/857092723/</t>
         </is>
       </c>
     </row>
@@ -23238,12 +23238,12 @@
       </c>
       <c r="C616" s="2" t="inlineStr">
         <is>
-          <t>Facilities Planning Engineer</t>
+          <t>Upstream &amp; LNG Strategist</t>
         </is>
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>UR Proj Mgmt &amp; Tech Services Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E616" s="2" t="inlineStr">
@@ -23253,12 +23253,12 @@
       </c>
       <c r="F616" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G616" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16984</t>
+          <t>https://careers.aramco.com/expat_uk/job/Upstream-&amp;-LNG-Strategist/857093323/</t>
         </is>
       </c>
     </row>
@@ -23275,12 +23275,12 @@
       </c>
       <c r="C617" s="3" t="inlineStr">
         <is>
-          <t>Production Engineer</t>
+          <t>Process Engineer - Solomon Benchmarking - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D617" s="3" t="inlineStr">
         <is>
-          <t>UR Production Engrg Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E617" s="3" t="inlineStr">
@@ -23290,12 +23290,12 @@
       </c>
       <c r="F617" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G617" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17321</t>
+          <t>https://careers.aramco.com/expat_us/job/Process-Engineer-Solomon-Benchmarking-Refinery-Experience-Only/855870823/</t>
         </is>
       </c>
     </row>
@@ -23312,12 +23312,12 @@
       </c>
       <c r="C618" s="2" t="inlineStr">
         <is>
-          <t>Lead Corporate Strategist - Industrial Portfolio</t>
+          <t>Compliance Counsel</t>
         </is>
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E618" s="2" t="inlineStr">
@@ -23327,12 +23327,12 @@
       </c>
       <c r="F618" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17678</t>
+          <t>https://careers.aramco.com/expat_us/job/Compliance-Counsel/857119823/</t>
         </is>
       </c>
     </row>
@@ -23349,12 +23349,12 @@
       </c>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>Sr Legal Counsel - Gas</t>
+          <t>Accounting Analyst</t>
         </is>
       </c>
       <c r="D619" s="3" t="inlineStr">
         <is>
-          <t>Upstream Law Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E619" s="3" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G619" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16873</t>
+          <t>https://careers.aramco.com/expat_uk/job/Accounting-Analyst/857119923/</t>
         </is>
       </c>
     </row>
@@ -23386,12 +23386,12 @@
       </c>
       <c r="C620" s="2" t="inlineStr">
         <is>
-          <t>Sr Power Systems Strategy &amp; Market Consultant</t>
+          <t>Elementary-Intermediate Teacher</t>
         </is>
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>Power Systems Planning Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E620" s="2" t="inlineStr">
@@ -23401,12 +23401,12 @@
       </c>
       <c r="F620" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17033</t>
+          <t>https://careers.aramco.com/expat_us/job/Elementary-Intermediate-Teacher/857066723/</t>
         </is>
       </c>
     </row>
@@ -23423,12 +23423,12 @@
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>Business Origination Specialist</t>
+          <t>Lead Field Compliance Coordinator</t>
         </is>
       </c>
       <c r="D621" s="3" t="inlineStr">
         <is>
-          <t>Origination&amp;Portfolio Optimization Dept</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E621" s="3" t="inlineStr">
@@ -23438,12 +23438,12 @@
       </c>
       <c r="F621" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G621" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17247</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Field-Compliance-Coordinator/857067423/</t>
         </is>
       </c>
     </row>
@@ -23460,12 +23460,12 @@
       </c>
       <c r="C622" s="2" t="inlineStr">
         <is>
-          <t>Sr Legal Counsel - Unconventional Gas</t>
+          <t>Business Development Specialist - Transaction &amp; Execution</t>
         </is>
       </c>
       <c r="D622" s="2" t="inlineStr">
         <is>
-          <t>Upstream Law Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E622" s="2" t="inlineStr">
@@ -23475,12 +23475,12 @@
       </c>
       <c r="F622" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G622" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16874</t>
+          <t>https://careers.aramco.com/expat_uk/job/Business-Development-Specialist-Transaction-&amp;-Execution/857091523/</t>
         </is>
       </c>
     </row>
@@ -23497,12 +23497,12 @@
       </c>
       <c r="C623" s="3" t="inlineStr">
         <is>
-          <t>Sr Counsel - Chemicals &amp; Retail</t>
+          <t>AI Governance Officer</t>
         </is>
       </c>
       <c r="D623" s="3" t="inlineStr">
         <is>
-          <t>Products &amp; Customers Law Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E623" s="3" t="inlineStr">
@@ -23512,12 +23512,12 @@
       </c>
       <c r="F623" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G623" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16865</t>
+          <t>https://careers.aramco.com/expat_uk/job/AI-Governance-Officer/856776223/</t>
         </is>
       </c>
     </row>
@@ -23534,12 +23534,12 @@
       </c>
       <c r="C624" s="2" t="inlineStr">
         <is>
-          <t>Computational Research Expert (Optimization and Control)</t>
+          <t>Speechwriter</t>
         </is>
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>Research &amp; Dev Center Department</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E624" s="2" t="inlineStr">
@@ -23549,12 +23549,12 @@
       </c>
       <c r="F624" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17281</t>
+          <t>https://careers.aramco.com/expat_us/job/Speechwriter/857091923/</t>
         </is>
       </c>
     </row>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>Computational Research Expert (AI Specialist)</t>
+          <t>Affiliates Management Advisor - Medical Services</t>
         </is>
       </c>
       <c r="D625" s="3" t="inlineStr">
         <is>
-          <t>Research &amp; Dev Center Department</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E625" s="3" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="F625" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G625" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17280</t>
+          <t>https://careers.aramco.com/expat_uk/job/Affiliates-Management-Advisor-Medical-Services/857091823/</t>
         </is>
       </c>
     </row>
@@ -23608,12 +23608,12 @@
       </c>
       <c r="C626" s="2" t="inlineStr">
         <is>
-          <t>Electrical Power Contracts Engineer</t>
+          <t>Mineral Strategy Analyst</t>
         </is>
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>Power Systems Planning Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E626" s="2" t="inlineStr">
@@ -23623,12 +23623,12 @@
       </c>
       <c r="F626" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G626" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17034</t>
+          <t>https://careers.aramco.com/expat_us/job/Mineral-Strategy-Analyst/857119423/</t>
         </is>
       </c>
     </row>
@@ -23645,12 +23645,12 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>Other Graduates (less than three years of work experience)</t>
+          <t>Onshore Structural Engineer</t>
         </is>
       </c>
       <c r="D627" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E627" s="3" t="inlineStr">
@@ -23660,12 +23660,12 @@
       </c>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G627" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/1412</t>
+          <t>https://careers.aramco.com/expat_us/job/Onshore-Structural-Engineer/857089523/</t>
         </is>
       </c>
     </row>
@@ -23682,12 +23682,12 @@
       </c>
       <c r="C628" s="2" t="inlineStr">
         <is>
-          <t>Experienced IT (more than three years of work experience)</t>
+          <t>Business Development Specialist - Transaction Execution</t>
         </is>
       </c>
       <c r="D628" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E628" s="2" t="inlineStr">
@@ -23697,12 +23697,12 @@
       </c>
       <c r="F628" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G628" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16741</t>
+          <t>https://careers.aramco.com/expat_uk/job/Business-Development-Specialist-Transaction-Execution/857064923/</t>
         </is>
       </c>
     </row>
@@ -23719,12 +23719,12 @@
       </c>
       <c r="C629" s="3" t="inlineStr">
         <is>
-          <t>Counsel - General Corporate and Commercial Contracts</t>
+          <t>Lead Accounting Analyst</t>
         </is>
       </c>
       <c r="D629" s="3" t="inlineStr">
         <is>
-          <t>Gen Corp &amp; Commercial Law Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E629" s="3" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="F629" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G629" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16783</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Accounting-Analyst/856893023/</t>
         </is>
       </c>
     </row>
@@ -23756,12 +23756,12 @@
       </c>
       <c r="C630" s="2" t="inlineStr">
         <is>
-          <t>Experienced Engineer (more than three years of work experience)</t>
+          <t>Process Modeling Specialist</t>
         </is>
       </c>
       <c r="D630" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E630" s="2" t="inlineStr">
@@ -23771,12 +23771,12 @@
       </c>
       <c r="F630" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G630" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16740</t>
+          <t>https://careers.aramco.com/expat_us/job/Process-Modeling-Specialist/857089423/</t>
         </is>
       </c>
     </row>
@@ -23793,12 +23793,12 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>Experienced Business (more than three years of work experience)</t>
+          <t>Gas &amp; NGL Planning Engineer</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E631" s="3" t="inlineStr">
@@ -23808,12 +23808,12 @@
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16743</t>
+          <t>https://careers.aramco.com/expat_us/job/Gas-&amp;-NGL-Planning-Engineer/857089323/</t>
         </is>
       </c>
     </row>
@@ -23830,12 +23830,12 @@
       </c>
       <c r="C632" s="2" t="inlineStr">
         <is>
-          <t>Experienced Other (more than three years of work experience)</t>
+          <t>Process Simulation Twin &amp; Optimization Engineer - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D632" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E632" s="2" t="inlineStr">
@@ -23845,12 +23845,12 @@
       </c>
       <c r="F632" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G632" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16742</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Simulation-Twin-&amp;-Optimization-Engineer-Refinery-Experience-Only/857080823/</t>
         </is>
       </c>
     </row>
@@ -23867,12 +23867,12 @@
       </c>
       <c r="C633" s="3" t="inlineStr">
         <is>
-          <t>Assistant to Director</t>
+          <t>Sr Strategy &amp; Market Consultant</t>
         </is>
       </c>
       <c r="D633" s="3" t="inlineStr">
         <is>
-          <t>Office Services Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E633" s="3" t="inlineStr">
@@ -23882,12 +23882,12 @@
       </c>
       <c r="F633" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G633" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/1424</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Strategy-&amp;-Market-Consultant/857119023/</t>
         </is>
       </c>
     </row>
@@ -23904,12 +23904,12 @@
       </c>
       <c r="C634" s="2" t="inlineStr">
         <is>
-          <t>Occupational Health Consultant</t>
+          <t>Operational Excellence Specialist</t>
         </is>
       </c>
       <c r="D634" s="2" t="inlineStr">
         <is>
-          <t>Environmental Protection Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E634" s="2" t="inlineStr">
@@ -23919,12 +23919,12 @@
       </c>
       <c r="F634" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G634" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17393</t>
+          <t>https://careers.aramco.com/expat_us/job/Operational-Excellence-Specialist/857089023/</t>
         </is>
       </c>
     </row>
@@ -23941,12 +23941,12 @@
       </c>
       <c r="C635" s="3" t="inlineStr">
         <is>
-          <t>Senior Corporate Strategy Advisor</t>
+          <t>Instructional Designer</t>
         </is>
       </c>
       <c r="D635" s="3" t="inlineStr">
         <is>
-          <t>Corporate Sustainability Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E635" s="3" t="inlineStr">
@@ -23956,12 +23956,12 @@
       </c>
       <c r="F635" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G635" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16511</t>
+          <t>https://careers.aramco.com/expat_uk/job/Instructional-Designer/857088923/</t>
         </is>
       </c>
     </row>
@@ -23978,12 +23978,12 @@
       </c>
       <c r="C636" s="2" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Management and Decarbonization Specialist</t>
+          <t>Manufacturing Performance Expert - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>Green Energy &amp; Environmental Policy Dept</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E636" s="2" t="inlineStr">
@@ -23993,12 +23993,12 @@
       </c>
       <c r="F636" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G636" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17395</t>
+          <t>https://careers.aramco.com/expat_us/job/Manufacturing-Performance-Expert-Refinery-Experience-Only/855896223/</t>
         </is>
       </c>
     </row>
@@ -24015,12 +24015,12 @@
       </c>
       <c r="C637" s="3" t="inlineStr">
         <is>
-          <t>Pilot Plant Process Engineer</t>
+          <t>Field Compliance Coordinator</t>
         </is>
       </c>
       <c r="D637" s="3" t="inlineStr">
         <is>
-          <t>Research &amp; Analytical Services Dept</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E637" s="3" t="inlineStr">
@@ -24030,12 +24030,12 @@
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G637" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17216</t>
+          <t>https://careers.aramco.com/expat_uk/job/Field-Compliance-Coordinator/857117223/</t>
         </is>
       </c>
     </row>
@@ -24052,12 +24052,12 @@
       </c>
       <c r="C638" s="2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Facilities Planning Engineer</t>
         </is>
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E638" s="2" t="inlineStr">
@@ -24067,12 +24067,12 @@
       </c>
       <c r="F638" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G638" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17149</t>
+          <t>https://careers.aramco.com/expat_uk/job/Facilities-Planning-Engineer/857118423/</t>
         </is>
       </c>
     </row>
@@ -24089,12 +24089,12 @@
       </c>
       <c r="C639" s="3" t="inlineStr">
         <is>
-          <t>Process Engineer - Fluid Catalytic Cracking - Refinery Experience Only</t>
+          <t>Production Engineer</t>
         </is>
       </c>
       <c r="D639" s="3" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E639" s="3" t="inlineStr">
@@ -24104,12 +24104,12 @@
       </c>
       <c r="F639" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G639" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15350</t>
+          <t>https://careers.aramco.com/expat_uk/job/Production-Engineer/857117423/</t>
         </is>
       </c>
     </row>
@@ -24126,12 +24126,12 @@
       </c>
       <c r="C640" s="2" t="inlineStr">
         <is>
-          <t>Metering Engineer - Refinery Experience Only</t>
+          <t>Lead Corporate Strategist - Industrial Portfolio</t>
         </is>
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>Reliability Solutions Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E640" s="2" t="inlineStr">
@@ -24141,12 +24141,12 @@
       </c>
       <c r="F640" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G640" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15318</t>
+          <t>https://careers.aramco.com/expat_us/job/Lead-Corporate-Strategist-Industrial-Portfolio/857116623/</t>
         </is>
       </c>
     </row>
@@ -24163,12 +24163,12 @@
       </c>
       <c r="C641" s="3" t="inlineStr">
         <is>
-          <t>Oilfield Microbiology Specialist</t>
+          <t>Sr Legal Counsel - Gas</t>
         </is>
       </c>
       <c r="D641" s="3" t="inlineStr">
         <is>
-          <t>Research &amp; Analytical Services Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E641" s="3" t="inlineStr">
@@ -24178,12 +24178,12 @@
       </c>
       <c r="F641" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G641" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17277</t>
+          <t>https://careers.aramco.com/expat_us/job/Sr-Legal-Counsel-Gas/857013723/</t>
         </is>
       </c>
     </row>
@@ -24200,12 +24200,12 @@
       </c>
       <c r="C642" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Risk Management Specialist</t>
+          <t>Sr Power Systems Strategy &amp; Market Consultant</t>
         </is>
       </c>
       <c r="D642" s="2" t="inlineStr">
         <is>
-          <t>Decision Support &amp; Risk Mgmt Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E642" s="2" t="inlineStr">
@@ -24215,12 +24215,12 @@
       </c>
       <c r="F642" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G642" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17256</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Power-Systems-Strategy-&amp;-Market-Consultant/857062123/</t>
         </is>
       </c>
     </row>
@@ -24237,12 +24237,12 @@
       </c>
       <c r="C643" s="3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Business Origination Specialist</t>
         </is>
       </c>
       <c r="D643" s="3" t="inlineStr">
         <is>
-          <t>Global Optimizer Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E643" s="3" t="inlineStr">
@@ -24252,12 +24252,12 @@
       </c>
       <c r="F643" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G643" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17086</t>
+          <t>https://careers.aramco.com/expat_uk/job/Business-Origination-Specialist/857061923/</t>
         </is>
       </c>
     </row>
@@ -24274,12 +24274,12 @@
       </c>
       <c r="C644" s="2" t="inlineStr">
         <is>
-          <t>Financial Specialist</t>
+          <t>Sr Legal Counsel - Unconventional Gas</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
         <is>
-          <t>Group Treasury Mgmt Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E644" s="2" t="inlineStr">
@@ -24289,12 +24289,12 @@
       </c>
       <c r="F644" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G644" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16916</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Legal-Counsel-Unconventional-Gas/857013823/</t>
         </is>
       </c>
     </row>
@@ -24311,12 +24311,12 @@
       </c>
       <c r="C645" s="3" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Sr Counsel - Chemicals &amp; Retail</t>
         </is>
       </c>
       <c r="D645" s="3" t="inlineStr">
         <is>
-          <t>Fuels Strategy &amp; Capital Planning Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E645" s="3" t="inlineStr">
@@ -24326,12 +24326,12 @@
       </c>
       <c r="F645" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G645" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17085</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel-Chemicals-&amp;-Retail/857013923/</t>
         </is>
       </c>
     </row>
@@ -24348,12 +24348,12 @@
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>Data Management Analyst</t>
+          <t>Computational Research Expert (Optimization and Control)</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E646" s="2" t="inlineStr">
@@ -24363,12 +24363,12 @@
       </c>
       <c r="F646" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G646" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17009</t>
+          <t>https://careers.aramco.com/expat_uk/job/Computational-Research-Expert-%28Optimization-and-Control%29/857062823/</t>
         </is>
       </c>
     </row>
@@ -24385,12 +24385,12 @@
       </c>
       <c r="C647" s="3" t="inlineStr">
         <is>
-          <t>MV Switchgear Specialist</t>
+          <t>Computational Research Expert (AI Specialist)</t>
         </is>
       </c>
       <c r="D647" s="3" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E647" s="3" t="inlineStr">
@@ -24400,12 +24400,12 @@
       </c>
       <c r="F647" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G647" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17021</t>
+          <t>https://careers.aramco.com/expat_uk/job/Computational-Research-Expert-%28AI-Specialist%29/857062223/</t>
         </is>
       </c>
     </row>
@@ -24422,12 +24422,12 @@
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>Communications Specialist</t>
+          <t>Electrical Power Contracts Engineer</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
         <is>
-          <t>T&amp;I Business Support Dept</t>
+          <t>Contracts &amp; Procurement</t>
         </is>
       </c>
       <c r="E648" s="2" t="inlineStr">
@@ -24437,12 +24437,12 @@
       </c>
       <c r="F648" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G648" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17157</t>
+          <t>https://careers.aramco.com/expat_uk/job/Electrical-Power-Contracts-Engineer/857062023/</t>
         </is>
       </c>
     </row>
@@ -24459,12 +24459,12 @@
       </c>
       <c r="C649" s="3" t="inlineStr">
         <is>
-          <t>Downstream Corrosion Engineer - Refinery Experience Only</t>
+          <t>Other Graduates (less than three years of work experience)</t>
         </is>
       </c>
       <c r="D649" s="3" t="inlineStr">
         <is>
-          <t>Reliability Solutions Dept</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E649" s="3" t="inlineStr">
@@ -24474,12 +24474,12 @@
       </c>
       <c r="F649" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G649" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15310</t>
+          <t>https://careers.aramco.com/saudi/job/Other-Graduates-%28less-than-three-years-of-work-experience%29/766636923/</t>
         </is>
       </c>
     </row>
@@ -24496,12 +24496,12 @@
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>Financial Auditor</t>
+          <t>Experienced IT (more than three years of work experience)</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
         <is>
-          <t>Projects Audits Dept</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E650" s="2" t="inlineStr">
@@ -24511,12 +24511,12 @@
       </c>
       <c r="F650" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G650" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16979</t>
+          <t>https://careers.aramco.com/saudi/job/Experienced-IT-%28more-than-three-years-of-work-experience%29/856956923/</t>
         </is>
       </c>
     </row>
@@ -24533,12 +24533,12 @@
       </c>
       <c r="C651" s="3" t="inlineStr">
         <is>
-          <t>Operational Auditor</t>
+          <t>Counsel - General Corporate and Commercial Contracts</t>
         </is>
       </c>
       <c r="D651" s="3" t="inlineStr">
         <is>
-          <t>Upstream Audits Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E651" s="3" t="inlineStr">
@@ -24548,12 +24548,12 @@
       </c>
       <c r="F651" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G651" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16975</t>
+          <t>https://careers.aramco.com/expat_uk/job/Counsel-General-Corporate-and-Commercial-Contracts/857013023/</t>
         </is>
       </c>
     </row>
@@ -24570,12 +24570,12 @@
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>Drilling Foreman</t>
+          <t>Experienced Engineer (more than three years of work experience)</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>UR Drilling 2 Dept</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E652" s="2" t="inlineStr">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="F652" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G652" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17062</t>
+          <t>https://careers.aramco.com/saudi/job/Experienced-Engineer-%28more-than-three-years-of-work-experience%29/856956723/</t>
         </is>
       </c>
     </row>
@@ -24607,12 +24607,12 @@
       </c>
       <c r="C653" s="3" t="inlineStr">
         <is>
-          <t>Drilling Foreman</t>
+          <t>Experienced Business (more than three years of work experience)</t>
         </is>
       </c>
       <c r="D653" s="3" t="inlineStr">
         <is>
-          <t>UR Drilling 2 Dept</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E653" s="3" t="inlineStr">
@@ -24622,12 +24622,12 @@
       </c>
       <c r="F653" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G653" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17064</t>
+          <t>https://careers.aramco.com/saudi/job/Experienced-Business-%28more-than-three-years-of-work-experience%29/856957123/</t>
         </is>
       </c>
     </row>
@@ -24644,12 +24644,12 @@
       </c>
       <c r="C654" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Experienced Other (more than three years of work experience)</t>
         </is>
       </c>
       <c r="D654" s="2" t="inlineStr">
         <is>
-          <t>Jafurah Gas Plant Dept</t>
+          <t>Early Careers</t>
         </is>
       </c>
       <c r="E654" s="2" t="inlineStr">
@@ -24659,12 +24659,12 @@
       </c>
       <c r="F654" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G654" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17022</t>
+          <t>https://careers.aramco.com/saudi/job/Experienced-Other-%28more-than-three-years-of-work-experience%29/856957023/</t>
         </is>
       </c>
     </row>
@@ -24681,12 +24681,12 @@
       </c>
       <c r="C655" s="3" t="inlineStr">
         <is>
-          <t>Instrumentation &amp; Control Engineer</t>
+          <t>Assistant to Director</t>
         </is>
       </c>
       <c r="D655" s="3" t="inlineStr">
         <is>
-          <t>Hawiyah Gas Plant Department</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E655" s="3" t="inlineStr">
@@ -24696,12 +24696,12 @@
       </c>
       <c r="F655" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G655" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17024</t>
+          <t>https://careers.aramco.com/expat_uk/job/Assistant-to-Director/766671423/</t>
         </is>
       </c>
     </row>
@@ -24718,12 +24718,12 @@
       </c>
       <c r="C656" s="2" t="inlineStr">
         <is>
-          <t>Drilling Foreman</t>
+          <t>Occupational Health Consultant</t>
         </is>
       </c>
       <c r="D656" s="2" t="inlineStr">
         <is>
-          <t>UR Drilling 2 Dept</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E656" s="2" t="inlineStr">
@@ -24733,12 +24733,12 @@
       </c>
       <c r="F656" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G656" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17063</t>
+          <t>https://careers.aramco.com/expat_us/job/Occupational-Health-Consultant/857088023/</t>
         </is>
       </c>
     </row>
@@ -24755,12 +24755,12 @@
       </c>
       <c r="C657" s="3" t="inlineStr">
         <is>
-          <t>IT Auditor</t>
+          <t>Senior Corporate Strategy Advisor</t>
         </is>
       </c>
       <c r="D657" s="3" t="inlineStr">
         <is>
-          <t>Projects Audits Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E657" s="3" t="inlineStr">
@@ -24770,12 +24770,12 @@
       </c>
       <c r="F657" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G657" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16980</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Corporate-Strategy-Advisor/856748923/</t>
         </is>
       </c>
     </row>
@@ -24792,12 +24792,12 @@
       </c>
       <c r="C658" s="2" t="inlineStr">
         <is>
-          <t>Rotating Equipment Engineer</t>
+          <t>Greenhouse Gas Management and Decarbonization Specialist</t>
         </is>
       </c>
       <c r="D658" s="2" t="inlineStr">
         <is>
-          <t>Riyas NGL Fractionation Dept</t>
+          <t>Environmental &amp; Sustainability</t>
         </is>
       </c>
       <c r="E658" s="2" t="inlineStr">
@@ -24807,12 +24807,12 @@
       </c>
       <c r="F658" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G658" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17006</t>
+          <t>https://careers.aramco.com/expat_us/job/Greenhouse-Gas-Management-and-Decarbonization-Specialist/857088123/</t>
         </is>
       </c>
     </row>
@@ -24829,12 +24829,12 @@
       </c>
       <c r="C659" s="3" t="inlineStr">
         <is>
-          <t>Protection &amp; Control Engineer</t>
+          <t>Pilot Plant Process Engineer</t>
         </is>
       </c>
       <c r="D659" s="3" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E659" s="3" t="inlineStr">
@@ -24844,12 +24844,12 @@
       </c>
       <c r="F659" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G659" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17015</t>
+          <t>https://careers.aramco.com/expat_uk/job/Pilot-Plant-Process-Engineer/857061123/</t>
         </is>
       </c>
     </row>
@@ -24866,12 +24866,12 @@
       </c>
       <c r="C660" s="2" t="inlineStr">
         <is>
-          <t>Drilling Foreman</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="D660" s="2" t="inlineStr">
         <is>
-          <t>Offshore Drilling Dept # 1</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E660" s="2" t="inlineStr">
@@ -24881,12 +24881,12 @@
       </c>
       <c r="F660" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G660" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17165</t>
+          <t>https://careers.aramco.com/expat_uk/job/Data-Scientist/857061023/</t>
         </is>
       </c>
     </row>
@@ -24903,12 +24903,12 @@
       </c>
       <c r="C661" s="3" t="inlineStr">
         <is>
-          <t>Rotating Equipment Engineer</t>
+          <t>Process Engineer - Fluid Catalytic Cracking - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D661" s="3" t="inlineStr">
         <is>
-          <t>UR Producing Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E661" s="3" t="inlineStr">
@@ -24918,12 +24918,12 @@
       </c>
       <c r="F661" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G661" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17011</t>
+          <t>https://careers.aramco.com/expat_us/job/Process-Engineer-Fluid-Catalytic-Cracking-Refinery-Experience-Only/855867223/</t>
         </is>
       </c>
     </row>
@@ -24940,12 +24940,12 @@
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Metering Engineer - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
-          <t>UR Producing Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E662" s="2" t="inlineStr">
@@ -24955,12 +24955,12 @@
       </c>
       <c r="F662" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G662" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17019</t>
+          <t>https://careers.aramco.com/expat_uk/job/Metering-Engineer-Refinery-Experience-Only/855916623/</t>
         </is>
       </c>
     </row>
@@ -24977,12 +24977,12 @@
       </c>
       <c r="C663" s="3" t="inlineStr">
         <is>
-          <t>Gas Insulated Switchgear Specialist</t>
+          <t>Oilfield Microbiology Specialist</t>
         </is>
       </c>
       <c r="D663" s="3" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E663" s="3" t="inlineStr">
@@ -24992,12 +24992,12 @@
       </c>
       <c r="F663" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G663" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17017</t>
+          <t>https://careers.aramco.com/expat_uk/job/Oilfield-Microbiology-Specialist/857060923/</t>
         </is>
       </c>
     </row>
@@ -25014,12 +25014,12 @@
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>Overhead Power Line Specialist</t>
+          <t>Enterprise Risk Management Specialist</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E664" s="2" t="inlineStr">
@@ -25029,12 +25029,12 @@
       </c>
       <c r="F664" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G664" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17016</t>
+          <t>https://careers.aramco.com/expat_us/job/Enterprise-Risk-Management-Specialist/857044623/</t>
         </is>
       </c>
     </row>
@@ -25051,12 +25051,12 @@
       </c>
       <c r="C665" s="3" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="D665" s="3" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E665" s="3" t="inlineStr">
@@ -25066,12 +25066,12 @@
       </c>
       <c r="F665" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G665" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17020</t>
+          <t>https://careers.aramco.com/expat_us/job/Data-Scientist/857087823/</t>
         </is>
       </c>
     </row>
@@ -25088,12 +25088,12 @@
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>Turnaround &amp; Inspection Engineer</t>
+          <t>Financial Specialist</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
         <is>
-          <t>Riyas NGL Fractionation Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E666" s="2" t="inlineStr">
@@ -25103,12 +25103,12 @@
       </c>
       <c r="F666" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G666" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17007</t>
+          <t>https://careers.aramco.com/expat_uk/job/Financial-Specialist/857040523/</t>
         </is>
       </c>
     </row>
@@ -25125,12 +25125,12 @@
       </c>
       <c r="C667" s="3" t="inlineStr">
         <is>
-          <t>Plant Corrosion Engineer</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="D667" s="3" t="inlineStr">
         <is>
-          <t>Tanajib Gas Plant Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E667" s="3" t="inlineStr">
@@ -25140,12 +25140,12 @@
       </c>
       <c r="F667" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G667" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17061</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Engineer/857087723/</t>
         </is>
       </c>
     </row>
@@ -25162,12 +25162,12 @@
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>Electrical Engineer</t>
+          <t>Data Management Analyst</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
         <is>
-          <t>UR Producing Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E668" s="2" t="inlineStr">
@@ -25177,12 +25177,12 @@
       </c>
       <c r="F668" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G668" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17014</t>
+          <t>https://careers.aramco.com/expat_us/job/Data-Management-Analyst/857087423/</t>
         </is>
       </c>
     </row>
@@ -25199,12 +25199,12 @@
       </c>
       <c r="C669" s="3" t="inlineStr">
         <is>
-          <t>Fraud Investigator</t>
+          <t>MV Switchgear Specialist</t>
         </is>
       </c>
       <c r="D669" s="3" t="inlineStr">
         <is>
-          <t>Projects Audits Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E669" s="3" t="inlineStr">
@@ -25214,12 +25214,12 @@
       </c>
       <c r="F669" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G669" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16981</t>
+          <t>https://careers.aramco.com/expat_uk/job/MV-Switchgear-Specialist/857087323/</t>
         </is>
       </c>
     </row>
@@ -25236,12 +25236,12 @@
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>Plant Corrosion Engineer</t>
+          <t>Communications Specialist</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
         <is>
-          <t>Riyas NGL Fractionation Dept</t>
+          <t>Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="E670" s="2" t="inlineStr">
@@ -25251,12 +25251,12 @@
       </c>
       <c r="F670" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G670" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17008</t>
+          <t>https://careers.aramco.com/expat_uk/job/Communications-Specialist/857087523/</t>
         </is>
       </c>
     </row>
@@ -25273,12 +25273,12 @@
       </c>
       <c r="C671" s="3" t="inlineStr">
         <is>
-          <t>Reliability &amp; Asset Integrity Engineer</t>
+          <t>Downstream Corrosion Engineer - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D671" s="3" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E671" s="3" t="inlineStr">
@@ -25288,12 +25288,12 @@
       </c>
       <c r="F671" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G671" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17010</t>
+          <t>https://careers.aramco.com/expat_uk/job/Downstream-Corrosion-Engineer-Refinery-Experience-Only/855852423/</t>
         </is>
       </c>
     </row>
@@ -25310,12 +25310,12 @@
       </c>
       <c r="C672" s="2" t="inlineStr">
         <is>
-          <t>Reservoir Engineer</t>
+          <t>Financial Auditor</t>
         </is>
       </c>
       <c r="D672" s="2" t="inlineStr">
         <is>
-          <t>Unconventional Reservoir Engrg Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E672" s="2" t="inlineStr">
@@ -25325,12 +25325,12 @@
       </c>
       <c r="F672" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G672" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17030</t>
+          <t>https://careers.aramco.com/expat_uk/job/Financial-Auditor/857038223/</t>
         </is>
       </c>
     </row>
@@ -25347,12 +25347,12 @@
       </c>
       <c r="C673" s="3" t="inlineStr">
         <is>
-          <t>Static Mechanical Engineer</t>
+          <t>Operational Auditor</t>
         </is>
       </c>
       <c r="D673" s="3" t="inlineStr">
         <is>
-          <t>Jafurah Gas Plant Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E673" s="3" t="inlineStr">
@@ -25362,12 +25362,12 @@
       </c>
       <c r="F673" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G673" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17023</t>
+          <t>https://careers.aramco.com/expat_us/job/Operational-Auditor/857038523/</t>
         </is>
       </c>
     </row>
@@ -25384,12 +25384,12 @@
       </c>
       <c r="C674" s="2" t="inlineStr">
         <is>
-          <t>Continuous Improvement Consultant</t>
+          <t>Drilling Foreman</t>
         </is>
       </c>
       <c r="D674" s="2" t="inlineStr">
         <is>
-          <t>Group Transformation &amp; Advisory Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E674" s="2" t="inlineStr">
@@ -25399,12 +25399,12 @@
       </c>
       <c r="F674" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G674" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17185</t>
+          <t>https://careers.aramco.com/expat_uk/job/Drilling-Foreman/857038623/</t>
         </is>
       </c>
     </row>
@@ -25421,12 +25421,12 @@
       </c>
       <c r="C675" s="3" t="inlineStr">
         <is>
-          <t>Power Cable Specialist</t>
+          <t>Drilling Foreman</t>
         </is>
       </c>
       <c r="D675" s="3" t="inlineStr">
         <is>
-          <t>Power Systems Projects &amp; Tech Supp Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E675" s="3" t="inlineStr">
@@ -25436,12 +25436,12 @@
       </c>
       <c r="F675" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G675" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17018</t>
+          <t>https://careers.aramco.com/expat_uk/job/Drilling-Foreman/857038823/</t>
         </is>
       </c>
     </row>
@@ -25458,12 +25458,12 @@
       </c>
       <c r="C676" s="2" t="inlineStr">
         <is>
-          <t>Strategic Workforce Planning Consultant</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="D676" s="2" t="inlineStr">
         <is>
-          <t>Organization Consulting Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E676" s="2" t="inlineStr">
@@ -25473,12 +25473,12 @@
       </c>
       <c r="F676" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G676" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17478</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Engineer/857039823/</t>
         </is>
       </c>
     </row>
@@ -25495,12 +25495,12 @@
       </c>
       <c r="C677" s="3" t="inlineStr">
         <is>
-          <t>Executive Assessment Lead</t>
+          <t>Instrumentation &amp; Control Engineer</t>
         </is>
       </c>
       <c r="D677" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E677" s="3" t="inlineStr">
@@ -25510,12 +25510,12 @@
       </c>
       <c r="F677" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G677" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17234</t>
+          <t>https://careers.aramco.com/expat_uk/job/Instrumentation-&amp;-Control-Engineer/857039023/</t>
         </is>
       </c>
     </row>
@@ -25532,12 +25532,12 @@
       </c>
       <c r="C678" s="2" t="inlineStr">
         <is>
-          <t>Sr Counsel I</t>
+          <t>Drilling Foreman</t>
         </is>
       </c>
       <c r="D678" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E678" s="2" t="inlineStr">
@@ -25547,12 +25547,12 @@
       </c>
       <c r="F678" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G678" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16801</t>
+          <t>https://careers.aramco.com/expat_uk/job/Drilling-Foreman/857038723/</t>
         </is>
       </c>
     </row>
@@ -25569,12 +25569,12 @@
       </c>
       <c r="C679" s="3" t="inlineStr">
         <is>
-          <t>Computational Research Expert (Material Discovery)</t>
+          <t>IT Auditor</t>
         </is>
       </c>
       <c r="D679" s="3" t="inlineStr">
         <is>
-          <t>Research &amp; Dev Center Department</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E679" s="3" t="inlineStr">
@@ -25584,12 +25584,12 @@
       </c>
       <c r="F679" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G679" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17278</t>
+          <t>https://careers.aramco.com/expat_uk/job/IT-Auditor/857038423/</t>
         </is>
       </c>
     </row>
@@ -25606,12 +25606,12 @@
       </c>
       <c r="C680" s="2" t="inlineStr">
         <is>
-          <t>Electrical Project Engineer</t>
+          <t>Rotating Equipment Engineer</t>
         </is>
       </c>
       <c r="D680" s="2" t="inlineStr">
         <is>
-          <t>UR Proj Mgmt &amp; Tech Services Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E680" s="2" t="inlineStr">
@@ -25621,12 +25621,12 @@
       </c>
       <c r="F680" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G680" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16982</t>
+          <t>https://careers.aramco.com/expat_uk/job/Rotating-Equipment-Engineer/857039523/</t>
         </is>
       </c>
     </row>
@@ -25643,12 +25643,12 @@
       </c>
       <c r="C681" s="3" t="inlineStr">
         <is>
-          <t>Lead Mechanical Project Engineer</t>
+          <t>Protection &amp; Control Engineer</t>
         </is>
       </c>
       <c r="D681" s="3" t="inlineStr">
         <is>
-          <t>UR Proj Mgmt &amp; Tech Services Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E681" s="3" t="inlineStr">
@@ -25658,12 +25658,12 @@
       </c>
       <c r="F681" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G681" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16972</t>
+          <t>https://careers.aramco.com/expat_us/job/Protection-&amp;-Control-Engineer/857086823/</t>
         </is>
       </c>
     </row>
@@ -25680,12 +25680,12 @@
       </c>
       <c r="C682" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Project Engineer</t>
+          <t>Drilling Foreman</t>
         </is>
       </c>
       <c r="D682" s="2" t="inlineStr">
         <is>
-          <t>UR Proj Mgmt &amp; Tech Services Dept</t>
+          <t>Drilling &amp; Production</t>
         </is>
       </c>
       <c r="E682" s="2" t="inlineStr">
@@ -25695,12 +25695,12 @@
       </c>
       <c r="F682" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G682" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16983</t>
+          <t>https://careers.aramco.com/expat_us/job/Drilling-Foreman/857086623/</t>
         </is>
       </c>
     </row>
@@ -25717,12 +25717,12 @@
       </c>
       <c r="C683" s="3" t="inlineStr">
         <is>
-          <t>Downstream Sustainability Specialist</t>
+          <t>Rotating Equipment Engineer</t>
         </is>
       </c>
       <c r="D683" s="3" t="inlineStr">
         <is>
-          <t>Downstream Strategy &amp; Capital Plng Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E683" s="3" t="inlineStr">
@@ -25732,12 +25732,12 @@
       </c>
       <c r="F683" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G683" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17413</t>
+          <t>https://careers.aramco.com/expat_uk/job/Rotating-Equipment-Engineer/857039623/</t>
         </is>
       </c>
     </row>
@@ -25754,12 +25754,12 @@
       </c>
       <c r="C684" s="2" t="inlineStr">
         <is>
-          <t>Planning &amp; Performance Analyst</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="D684" s="2" t="inlineStr">
         <is>
-          <t>Global Mfg Plng &amp; Perf Mgmt Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E684" s="2" t="inlineStr">
@@ -25769,12 +25769,12 @@
       </c>
       <c r="F684" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G684" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17423</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Engineer/857039323/</t>
         </is>
       </c>
     </row>
@@ -25791,12 +25791,12 @@
       </c>
       <c r="C685" s="3" t="inlineStr">
         <is>
-          <t>Accounting Analyst</t>
+          <t>Gas Insulated Switchgear Specialist</t>
         </is>
       </c>
       <c r="D685" s="3" t="inlineStr">
         <is>
-          <t>Downstream Fin Plng &amp; Perf Mgmt Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E685" s="3" t="inlineStr">
@@ -25806,12 +25806,12 @@
       </c>
       <c r="F685" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G685" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17421</t>
+          <t>https://careers.aramco.com/expat_us/job/Gas-Insulated-Switchgear-Specialist/857086923/</t>
         </is>
       </c>
     </row>
@@ -25828,12 +25828,12 @@
       </c>
       <c r="C686" s="2" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas Financial Analyst</t>
+          <t>Overhead Power Line Specialist</t>
         </is>
       </c>
       <c r="D686" s="2" t="inlineStr">
         <is>
-          <t>Downstream Strategy &amp; Capital Plng Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E686" s="2" t="inlineStr">
@@ -25843,12 +25843,12 @@
       </c>
       <c r="F686" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G686" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17415</t>
+          <t>https://careers.aramco.com/expat_us/job/Overhead-Power-Line-Specialist/857086723/</t>
         </is>
       </c>
     </row>
@@ -25865,12 +25865,12 @@
       </c>
       <c r="C687" s="3" t="inlineStr">
         <is>
-          <t>Senior Downstream Planning &amp; Performance Management Analyst</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="D687" s="3" t="inlineStr">
         <is>
-          <t>Downstream Fin Plng &amp; Perf Mgmt Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E687" s="3" t="inlineStr">
@@ -25880,12 +25880,12 @@
       </c>
       <c r="F687" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G687" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17420</t>
+          <t>https://careers.aramco.com/expat_uk/job/Automation-Engineer/857087023/</t>
         </is>
       </c>
     </row>
@@ -25902,12 +25902,12 @@
       </c>
       <c r="C688" s="2" t="inlineStr">
         <is>
-          <t>Governance, Risk &amp; Compliance Specialist</t>
+          <t>Turnaround &amp; Inspection Engineer</t>
         </is>
       </c>
       <c r="D688" s="2" t="inlineStr">
         <is>
-          <t>D&amp;IT Strategy &amp; Investment Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E688" s="2" t="inlineStr">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="F688" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G688" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17608</t>
+          <t>https://careers.aramco.com/expat_uk/job/Turnaround-&amp;-Inspection-Engineer/857039723/</t>
         </is>
       </c>
     </row>
@@ -25939,12 +25939,12 @@
       </c>
       <c r="C689" s="3" t="inlineStr">
         <is>
-          <t>Lead Financial Reporting &amp; Performance Analyst</t>
+          <t>Plant Corrosion Engineer</t>
         </is>
       </c>
       <c r="D689" s="3" t="inlineStr">
         <is>
-          <t>Downstream Fin Plng &amp; Perf Mgmt Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E689" s="3" t="inlineStr">
@@ -25954,12 +25954,12 @@
       </c>
       <c r="F689" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G689" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17418</t>
+          <t>https://careers.aramco.com/expat_uk/job/Plant-Corrosion-Engineer/857039223/</t>
         </is>
       </c>
     </row>
@@ -25976,12 +25976,12 @@
       </c>
       <c r="C690" s="2" t="inlineStr">
         <is>
-          <t>Lead Downstream Finance, Planning &amp; Performance Management Analyst</t>
+          <t>Electrical Engineer</t>
         </is>
       </c>
       <c r="D690" s="2" t="inlineStr">
         <is>
-          <t>Downstream Fin Plng &amp; Perf Mgmt Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E690" s="2" t="inlineStr">
@@ -25991,12 +25991,12 @@
       </c>
       <c r="F690" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G690" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17419</t>
+          <t>https://careers.aramco.com/expat_uk/job/Electrical-Engineer/857038923/</t>
         </is>
       </c>
     </row>
@@ -26013,12 +26013,12 @@
       </c>
       <c r="C691" s="3" t="inlineStr">
         <is>
-          <t>Senior Planning &amp; Performance Management Advisor</t>
+          <t>Fraud Investigator</t>
         </is>
       </c>
       <c r="D691" s="3" t="inlineStr">
         <is>
-          <t>Products &amp; Cust Plng &amp; Perf Mgmt Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E691" s="3" t="inlineStr">
@@ -26028,12 +26028,12 @@
       </c>
       <c r="F691" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G691" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17416</t>
+          <t>https://careers.aramco.com/expat_uk/job/Fraud-Investigator/857038323/</t>
         </is>
       </c>
     </row>
@@ -26050,12 +26050,12 @@
       </c>
       <c r="C692" s="2" t="inlineStr">
         <is>
-          <t>Banking Operations Specialist</t>
+          <t>Plant Corrosion Engineer</t>
         </is>
       </c>
       <c r="D692" s="2" t="inlineStr">
         <is>
-          <t>Group Treasury Mgmt Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E692" s="2" t="inlineStr">
@@ -26065,12 +26065,12 @@
       </c>
       <c r="F692" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G692" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17146</t>
+          <t>https://careers.aramco.com/expat_uk/job/Plant-Corrosion-Engineer/857039123/</t>
         </is>
       </c>
     </row>
@@ -26087,12 +26087,12 @@
       </c>
       <c r="C693" s="3" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Reliability &amp; Asset Integrity Engineer</t>
         </is>
       </c>
       <c r="D693" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Environmental &amp; Sustainability</t>
         </is>
       </c>
       <c r="E693" s="3" t="inlineStr">
@@ -26102,12 +26102,12 @@
       </c>
       <c r="F693" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G693" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17357</t>
+          <t>https://careers.aramco.com/expat_us/job/Reliability-&amp;-Asset-Integrity-Engineer/857086223/</t>
         </is>
       </c>
     </row>
@@ -26124,12 +26124,12 @@
       </c>
       <c r="C694" s="2" t="inlineStr">
         <is>
-          <t>Rotating Equipment Engineer</t>
+          <t>Reservoir Engineer</t>
         </is>
       </c>
       <c r="D694" s="2" t="inlineStr">
         <is>
-          <t>Yanbu Refinery Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E694" s="2" t="inlineStr">
@@ -26139,12 +26139,12 @@
       </c>
       <c r="F694" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G694" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17172</t>
+          <t>https://careers.aramco.com/expat_uk/job/Reservoir-Engineer/857039423/</t>
         </is>
       </c>
     </row>
@@ -26161,12 +26161,12 @@
       </c>
       <c r="C695" s="3" t="inlineStr">
         <is>
-          <t>Contracts Advisor</t>
+          <t>Static Mechanical Engineer</t>
         </is>
       </c>
       <c r="D695" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E695" s="3" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="F695" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G695" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17356</t>
+          <t>https://careers.aramco.com/expat_uk/job/Static-Mechanical-Engineer/857039923/</t>
         </is>
       </c>
     </row>
@@ -26198,12 +26198,12 @@
       </c>
       <c r="C696" s="2" t="inlineStr">
         <is>
-          <t>Business Development Specialist</t>
+          <t>Continuous Improvement Consultant</t>
         </is>
       </c>
       <c r="D696" s="2" t="inlineStr">
         <is>
-          <t>Downstream Transaction Development Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E696" s="2" t="inlineStr">
@@ -26213,12 +26213,12 @@
       </c>
       <c r="F696" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G696" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17140</t>
+          <t>https://careers.aramco.com/expat_uk/job/Continuous-Improvement-Consultant/857086123/</t>
         </is>
       </c>
     </row>
@@ -26235,12 +26235,12 @@
       </c>
       <c r="C697" s="3" t="inlineStr">
         <is>
-          <t>Business Development Specialist</t>
+          <t>Power Cable Specialist</t>
         </is>
       </c>
       <c r="D697" s="3" t="inlineStr">
         <is>
-          <t>Downstream Origination Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E697" s="3" t="inlineStr">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="F697" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G697" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17139</t>
+          <t>https://careers.aramco.com/expat_uk/job/Power-Cable-Specialist/857087123/</t>
         </is>
       </c>
     </row>
@@ -26272,12 +26272,12 @@
       </c>
       <c r="C698" s="2" t="inlineStr">
         <is>
-          <t>Human Factors Engineer</t>
+          <t>Strategic Workforce Planning Consultant</t>
         </is>
       </c>
       <c r="D698" s="2" t="inlineStr">
         <is>
-          <t>LP Technical Services Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E698" s="2" t="inlineStr">
@@ -26287,12 +26287,12 @@
       </c>
       <c r="F698" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G698" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17222</t>
+          <t>https://careers.aramco.com/expat_uk/job/Strategic-Workforce-Planning-Consultant/857085823/</t>
         </is>
       </c>
     </row>
@@ -26309,12 +26309,12 @@
       </c>
       <c r="C699" s="3" t="inlineStr">
         <is>
-          <t>Lead Organizational &amp; Management Specialist</t>
+          <t>Executive Assessment Lead</t>
         </is>
       </c>
       <c r="D699" s="3" t="inlineStr">
         <is>
-          <t>Organization Consulting Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E699" s="3" t="inlineStr">
@@ -26324,12 +26324,12 @@
       </c>
       <c r="F699" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G699" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17475</t>
+          <t>https://careers.aramco.com/expat_uk/job/Executive-Assessment-Lead/857085523/</t>
         </is>
       </c>
     </row>
@@ -26346,12 +26346,12 @@
       </c>
       <c r="C700" s="2" t="inlineStr">
         <is>
-          <t>Instructional Designer</t>
+          <t>Sr Counsel I</t>
         </is>
       </c>
       <c r="D700" s="2" t="inlineStr">
         <is>
-          <t>DS Learning &amp; Development Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E700" s="2" t="inlineStr">
@@ -26361,12 +26361,12 @@
       </c>
       <c r="F700" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G700" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16847</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel-I/857085023/</t>
         </is>
       </c>
     </row>
@@ -26383,12 +26383,12 @@
       </c>
       <c r="C701" s="3" t="inlineStr">
         <is>
-          <t>Incident Investigator</t>
+          <t>Computational Research Expert (Material Discovery)</t>
         </is>
       </c>
       <c r="D701" s="3" t="inlineStr">
         <is>
-          <t>LP Technical Services Dept</t>
+          <t>Digital &amp; IT</t>
         </is>
       </c>
       <c r="E701" s="3" t="inlineStr">
@@ -26398,12 +26398,12 @@
       </c>
       <c r="F701" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G701" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17219</t>
+          <t>https://careers.aramco.com/expat_uk/job/Computational-Research-Expert-%28Material-Discovery%29/857085923/</t>
         </is>
       </c>
     </row>
@@ -26420,12 +26420,12 @@
       </c>
       <c r="C702" s="2" t="inlineStr">
         <is>
-          <t>Emergency Management Advisor</t>
+          <t>Electrical Project Engineer</t>
         </is>
       </c>
       <c r="D702" s="2" t="inlineStr">
         <is>
-          <t>LP Technical Services Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E702" s="2" t="inlineStr">
@@ -26435,12 +26435,12 @@
       </c>
       <c r="F702" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G702" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17221</t>
+          <t>https://careers.aramco.com/expat_uk/job/Electrical-Project-Engineer/857109923/</t>
         </is>
       </c>
     </row>
@@ -26457,12 +26457,12 @@
       </c>
       <c r="C703" s="3" t="inlineStr">
         <is>
-          <t>Process/Operation Engineer</t>
+          <t>Lead Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="D703" s="3" t="inlineStr">
         <is>
-          <t>Learning Solutions &amp; Services Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E703" s="3" t="inlineStr">
@@ -26472,12 +26472,12 @@
       </c>
       <c r="F703" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G703" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17329</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Mechanical-Project-Engineer/857110023/</t>
         </is>
       </c>
     </row>
@@ -26494,12 +26494,12 @@
       </c>
       <c r="C704" s="2" t="inlineStr">
         <is>
-          <t>Program Development &amp; Evaluation Analyst</t>
+          <t>Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="D704" s="2" t="inlineStr">
         <is>
-          <t>Academic Programs &amp; Partnerships Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E704" s="2" t="inlineStr">
@@ -26509,12 +26509,12 @@
       </c>
       <c r="F704" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G704" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17375</t>
+          <t>https://careers.aramco.com/expat_uk/job/Mechanical-Project-Engineer/857109523/</t>
         </is>
       </c>
     </row>
@@ -26531,12 +26531,12 @@
       </c>
       <c r="C705" s="3" t="inlineStr">
         <is>
-          <t>Training &amp; Development Advisor</t>
+          <t>Downstream Sustainability Specialist</t>
         </is>
       </c>
       <c r="D705" s="3" t="inlineStr">
         <is>
-          <t>Academic Programs &amp; Partnerships Dept</t>
+          <t>Environmental &amp; Sustainability</t>
         </is>
       </c>
       <c r="E705" s="3" t="inlineStr">
@@ -26546,12 +26546,12 @@
       </c>
       <c r="F705" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G705" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17377</t>
+          <t>https://careers.aramco.com/expat_uk/job/Downstream-Sustainability-Specialist/857110723/</t>
         </is>
       </c>
     </row>
@@ -26568,12 +26568,12 @@
       </c>
       <c r="C706" s="2" t="inlineStr">
         <is>
-          <t>Reliability&amp;Rotating Equipment Engineer</t>
+          <t>Planning &amp; Performance Analyst</t>
         </is>
       </c>
       <c r="D706" s="2" t="inlineStr">
         <is>
-          <t>North Ghawar Producing Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E706" s="2" t="inlineStr">
@@ -26583,12 +26583,12 @@
       </c>
       <c r="F706" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G706" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16941</t>
+          <t>https://careers.aramco.com/expat_uk/job/Planning-&amp;-Performance-Analyst/857110423/</t>
         </is>
       </c>
     </row>
@@ -26605,12 +26605,12 @@
       </c>
       <c r="C707" s="3" t="inlineStr">
         <is>
-          <t>Intellectual Property Counsel</t>
+          <t>Accounting Analyst</t>
         </is>
       </c>
       <c r="D707" s="3" t="inlineStr">
         <is>
-          <t>Intellectual Property Law Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E707" s="3" t="inlineStr">
@@ -26620,12 +26620,12 @@
       </c>
       <c r="F707" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G707" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16811</t>
+          <t>https://careers.aramco.com/expat_uk/job/Accounting-Analyst/857110923/</t>
         </is>
       </c>
     </row>
@@ -26642,12 +26642,12 @@
       </c>
       <c r="C708" s="2" t="inlineStr">
         <is>
-          <t>Corrosion Engineer</t>
+          <t>Oil &amp; Gas Financial Analyst</t>
         </is>
       </c>
       <c r="D708" s="2" t="inlineStr">
         <is>
-          <t>SAOP Technical Support Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E708" s="2" t="inlineStr">
@@ -26657,12 +26657,12 @@
       </c>
       <c r="F708" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G708" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16940</t>
+          <t>https://careers.aramco.com/expat_uk/job/Oil-&amp;-Gas-Financial-Analyst/857110623/</t>
         </is>
       </c>
     </row>
@@ -26679,12 +26679,12 @@
       </c>
       <c r="C709" s="3" t="inlineStr">
         <is>
-          <t>Reservoir Engineer</t>
+          <t>Senior Downstream Planning &amp; Performance Management Analyst</t>
         </is>
       </c>
       <c r="D709" s="3" t="inlineStr">
         <is>
-          <t>Upstream Business Support Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E709" s="3" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="F709" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G709" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16883</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Downstream-Planning-&amp;-Performance-Management-Analyst/857109223/</t>
         </is>
       </c>
     </row>
@@ -26716,12 +26716,12 @@
       </c>
       <c r="C710" s="2" t="inlineStr">
         <is>
-          <t>Instrumentation Engineer</t>
+          <t>Governance, Risk &amp; Compliance Specialist</t>
         </is>
       </c>
       <c r="D710" s="2" t="inlineStr">
         <is>
-          <t>Abq Plants Operations Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E710" s="2" t="inlineStr">
@@ -26731,12 +26731,12 @@
       </c>
       <c r="F710" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G710" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16942</t>
+          <t>https://careers.aramco.com/expat_uk/job/Governance%2C-Risk-&amp;-Compliance-Specialist/857108723/</t>
         </is>
       </c>
     </row>
@@ -26753,12 +26753,12 @@
       </c>
       <c r="C711" s="3" t="inlineStr">
         <is>
-          <t>Sr Counsel</t>
+          <t>Lead Financial Reporting &amp; Performance Analyst</t>
         </is>
       </c>
       <c r="D711" s="3" t="inlineStr">
         <is>
-          <t>Gen Corp &amp; Commercial Law Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E711" s="3" t="inlineStr">
@@ -26768,12 +26768,12 @@
       </c>
       <c r="F711" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G711" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16840</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Financial-Reporting-&amp;-Performance-Analyst/857108423/</t>
         </is>
       </c>
     </row>
@@ -26790,12 +26790,12 @@
       </c>
       <c r="C712" s="2" t="inlineStr">
         <is>
-          <t>Exploration Geoscientist</t>
+          <t>Lead Downstream Finance, Planning &amp; Performance Management Analyst</t>
         </is>
       </c>
       <c r="D712" s="2" t="inlineStr">
         <is>
-          <t>Eastern Area Exploration Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E712" s="2" t="inlineStr">
@@ -26805,12 +26805,12 @@
       </c>
       <c r="F712" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G712" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16610</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Downstream-Finance%2C-Planning-&amp;-Performance-Management-Analyst/857108523/</t>
         </is>
       </c>
     </row>
@@ -26827,12 +26827,12 @@
       </c>
       <c r="C713" s="3" t="inlineStr">
         <is>
-          <t>Contracts Advisor</t>
+          <t>Senior Planning &amp; Performance Management Advisor</t>
         </is>
       </c>
       <c r="D713" s="3" t="inlineStr">
         <is>
-          <t>Marine Techl Support Dept</t>
+          <t>Strategy &amp; Planning</t>
         </is>
       </c>
       <c r="E713" s="3" t="inlineStr">
@@ -26842,12 +26842,12 @@
       </c>
       <c r="F713" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G713" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17325</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Planning-&amp;-Performance-Management-Advisor/857108323/</t>
         </is>
       </c>
     </row>
@@ -26864,12 +26864,12 @@
       </c>
       <c r="C714" s="2" t="inlineStr">
         <is>
-          <t>Delayed Coker Visbreaker Specialist - Refinery Experience Only</t>
+          <t>Banking Operations Specialist</t>
         </is>
       </c>
       <c r="D714" s="2" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Finance &amp; Audit</t>
         </is>
       </c>
       <c r="E714" s="2" t="inlineStr">
@@ -26879,12 +26879,12 @@
       </c>
       <c r="F714" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G714" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17353</t>
+          <t>https://careers.aramco.com/job/Banking-Operations-Specialist/857104823/</t>
         </is>
       </c>
     </row>
@@ -26901,12 +26901,12 @@
       </c>
       <c r="C715" s="3" t="inlineStr">
         <is>
-          <t>Technology Consultant - Refinery Experience Only</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="D715" s="3" t="inlineStr">
         <is>
-          <t>Tech &amp; Manufacturing Oversight Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E715" s="3" t="inlineStr">
@@ -26916,12 +26916,12 @@
       </c>
       <c r="F715" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G715" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17349</t>
+          <t>https://careers.aramco.com/expat_uk/job/Senior-Project-Engineer/857107623/</t>
         </is>
       </c>
     </row>
@@ -26938,12 +26938,12 @@
       </c>
       <c r="C716" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer - Utilities &amp; Tank Farm - Refinery Experience Only</t>
+          <t>Rotating Equipment Engineer</t>
         </is>
       </c>
       <c r="D716" s="2" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E716" s="2" t="inlineStr">
@@ -26953,12 +26953,12 @@
       </c>
       <c r="F716" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G716" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17355</t>
+          <t>https://careers.aramco.com/expat_uk/job/Rotating-Equipment-Engineer/857105623/</t>
         </is>
       </c>
     </row>
@@ -26975,12 +26975,12 @@
       </c>
       <c r="C717" s="3" t="inlineStr">
         <is>
-          <t>Process Engineer - Sulfur Recovery - Refinery Experience Only</t>
+          <t>Contracts Advisor</t>
         </is>
       </c>
       <c r="D717" s="3" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Contracts &amp; Procurement</t>
         </is>
       </c>
       <c r="E717" s="3" t="inlineStr">
@@ -26990,12 +26990,12 @@
       </c>
       <c r="F717" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G717" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17354</t>
+          <t>https://careers.aramco.com/expat_uk/job/Contracts-Advisor/857106023/</t>
         </is>
       </c>
     </row>
@@ -27012,12 +27012,12 @@
       </c>
       <c r="C718" s="2" t="inlineStr">
         <is>
-          <t>Analyzer Engineer - Refinery Experience Only</t>
+          <t>Business Development Specialist</t>
         </is>
       </c>
       <c r="D718" s="2" t="inlineStr">
         <is>
-          <t>Reliability Solutions Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E718" s="2" t="inlineStr">
@@ -27027,12 +27027,12 @@
       </c>
       <c r="F718" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G718" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17348</t>
+          <t>https://careers.aramco.com/expat_uk/job/Business-Development-Specialist/857038023/</t>
         </is>
       </c>
     </row>
@@ -27049,12 +27049,12 @@
       </c>
       <c r="C719" s="3" t="inlineStr">
         <is>
-          <t>Instrumentation Engineer - Refinery Experience Only</t>
+          <t>Business Development Specialist</t>
         </is>
       </c>
       <c r="D719" s="3" t="inlineStr">
         <is>
-          <t>Reliability Solutions Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E719" s="3" t="inlineStr">
@@ -27064,12 +27064,12 @@
       </c>
       <c r="F719" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G719" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17347</t>
+          <t>https://careers.aramco.com/expat_uk/job/Business-Development-Specialist/857037823/</t>
         </is>
       </c>
     </row>
@@ -27086,12 +27086,12 @@
       </c>
       <c r="C720" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Engineering Specialist - Refinery Experience Only</t>
+          <t>Human Factors Engineer</t>
         </is>
       </c>
       <c r="D720" s="2" t="inlineStr">
         <is>
-          <t>Maintenance Solutions Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E720" s="2" t="inlineStr">
@@ -27101,12 +27101,12 @@
       </c>
       <c r="F720" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G720" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17344</t>
+          <t>https://careers.aramco.com/expat_uk/job/Human-Factors-Engineer/857082323/</t>
         </is>
       </c>
     </row>
@@ -27123,12 +27123,12 @@
       </c>
       <c r="C721" s="3" t="inlineStr">
         <is>
-          <t>Lead Turnaround Engineer - Refinery Experience Only</t>
+          <t>Lead Organizational &amp; Management Specialist</t>
         </is>
       </c>
       <c r="D721" s="3" t="inlineStr">
         <is>
-          <t>Maintenance Solutions Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E721" s="3" t="inlineStr">
@@ -27138,12 +27138,12 @@
       </c>
       <c r="F721" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G721" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17345</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Organizational-&amp;-Management-Specialist/857083223/</t>
         </is>
       </c>
     </row>
@@ -27160,12 +27160,12 @@
       </c>
       <c r="C722" s="2" t="inlineStr">
         <is>
-          <t>Electrical Planning Engineer</t>
+          <t>Instructional Designer</t>
         </is>
       </c>
       <c r="D722" s="2" t="inlineStr">
         <is>
-          <t>Support Facilities Planning Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E722" s="2" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="F722" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G722" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17392</t>
+          <t>https://careers.aramco.com/expat_uk/job/Instructional-Designer/857036823/</t>
         </is>
       </c>
     </row>
@@ -27197,12 +27197,12 @@
       </c>
       <c r="C723" s="3" t="inlineStr">
         <is>
-          <t>Tax Counsel</t>
+          <t>Incident Investigator</t>
         </is>
       </c>
       <c r="D723" s="3" t="inlineStr">
         <is>
-          <t>Tax Law Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E723" s="3" t="inlineStr">
@@ -27212,12 +27212,12 @@
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G723" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16806</t>
+          <t>https://careers.aramco.com/expat_uk/job/Incident-Investigator/857082423/</t>
         </is>
       </c>
     </row>
@@ -27234,12 +27234,12 @@
       </c>
       <c r="C724" s="2" t="inlineStr">
         <is>
-          <t>Sr Counsel - Venture Capital</t>
+          <t>Emergency Management Advisor</t>
         </is>
       </c>
       <c r="D724" s="2" t="inlineStr">
         <is>
-          <t>Proj Development &amp; Finance Law Dept</t>
+          <t>Safety &amp; Security</t>
         </is>
       </c>
       <c r="E724" s="2" t="inlineStr">
@@ -27249,12 +27249,12 @@
       </c>
       <c r="F724" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G724" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16816</t>
+          <t>https://careers.aramco.com/expat_uk/job/Emergency-Management-Advisor/857082623/</t>
         </is>
       </c>
     </row>
@@ -27271,12 +27271,12 @@
       </c>
       <c r="C725" s="3" t="inlineStr">
         <is>
-          <t>Financial Auditor</t>
+          <t>Process/Operation Engineer</t>
         </is>
       </c>
       <c r="D725" s="3" t="inlineStr">
         <is>
-          <t>Upstream Audits Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E725" s="3" t="inlineStr">
@@ -27286,12 +27286,12 @@
       </c>
       <c r="F725" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G725" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16978</t>
+          <t>https://careers.aramco.com/expat_uk/job/ProcessOperation-Engineer/857082823/</t>
         </is>
       </c>
     </row>
@@ -27308,12 +27308,12 @@
       </c>
       <c r="C726" s="2" t="inlineStr">
         <is>
-          <t>Associate Counsel</t>
+          <t>Program Development &amp; Evaluation Analyst</t>
         </is>
       </c>
       <c r="D726" s="2" t="inlineStr">
         <is>
-          <t>Int'l Commercial Law Dept</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E726" s="2" t="inlineStr">
@@ -27323,12 +27323,12 @@
       </c>
       <c r="F726" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G726" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16834</t>
+          <t>https://careers.aramco.com/expat_uk/job/Program-Development-&amp;-Evaluation-Analyst/857083023/</t>
         </is>
       </c>
     </row>
@@ -27345,12 +27345,12 @@
       </c>
       <c r="C727" s="3" t="inlineStr">
         <is>
-          <t>Operational Auditor</t>
+          <t>Training &amp; Development Advisor</t>
         </is>
       </c>
       <c r="D727" s="3" t="inlineStr">
         <is>
-          <t>Upstream Audits Dept</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="E727" s="3" t="inlineStr">
@@ -27360,12 +27360,12 @@
       </c>
       <c r="F727" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G727" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16977</t>
+          <t>https://careers.aramco.com/expat_uk/job/Training-&amp;-Development-Advisor/857082923/</t>
         </is>
       </c>
     </row>
@@ -27382,12 +27382,12 @@
       </c>
       <c r="C728" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer - Hydrocracker - Refinery Experience Only</t>
+          <t>Reliability&amp;Rotating Equipment Engineer</t>
         </is>
       </c>
       <c r="D728" s="2" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E728" s="2" t="inlineStr">
@@ -27397,12 +27397,12 @@
       </c>
       <c r="F728" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G728" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15349</t>
+          <t>https://careers.aramco.com/expat_uk/job/Reliability&amp;Rotating-Equipment-Engineer/857036323/</t>
         </is>
       </c>
     </row>
@@ -27419,12 +27419,12 @@
       </c>
       <c r="C729" s="3" t="inlineStr">
         <is>
-          <t>Process Engineer - Hydrogen &amp; Naphtha - Refinery Experience Only</t>
+          <t>Intellectual Property Counsel</t>
         </is>
       </c>
       <c r="D729" s="3" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E729" s="3" t="inlineStr">
@@ -27434,12 +27434,12 @@
       </c>
       <c r="F729" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G729" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17352</t>
+          <t>https://careers.aramco.com/expat_uk/job/Intellectual-Property-Counsel/857034823/</t>
         </is>
       </c>
     </row>
@@ -27456,12 +27456,12 @@
       </c>
       <c r="C730" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer - Crude &amp; Vacuum - Refinery Experience Only</t>
+          <t>Corrosion Engineer</t>
         </is>
       </c>
       <c r="D730" s="2" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E730" s="2" t="inlineStr">
@@ -27471,12 +27471,12 @@
       </c>
       <c r="F730" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G730" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/15345</t>
+          <t>https://careers.aramco.com/expat_us/job/Corrosion-Engineer/857036423/</t>
         </is>
       </c>
     </row>
@@ -27493,12 +27493,12 @@
       </c>
       <c r="C731" s="3" t="inlineStr">
         <is>
-          <t>Cybersecurity Advisory Specialist</t>
+          <t>Reservoir Engineer</t>
         </is>
       </c>
       <c r="D731" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E731" s="3" t="inlineStr">
@@ -27508,12 +27508,12 @@
       </c>
       <c r="F731" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G731" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16636</t>
+          <t>https://careers.aramco.com/expat_us/job/Reservoir-Engineer/857035223/</t>
         </is>
       </c>
     </row>
@@ -27530,12 +27530,12 @@
       </c>
       <c r="C732" s="2" t="inlineStr">
         <is>
-          <t>Senior Operations Advisor</t>
+          <t>Instrumentation Engineer</t>
         </is>
       </c>
       <c r="D732" s="2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E732" s="2" t="inlineStr">
@@ -27545,12 +27545,12 @@
       </c>
       <c r="F732" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G732" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16639</t>
+          <t>https://careers.aramco.com/expat_us/job/Instrumentation-Engineer/857036523/</t>
         </is>
       </c>
     </row>
@@ -27567,12 +27567,12 @@
       </c>
       <c r="C733" s="3" t="inlineStr">
         <is>
-          <t>Lead IT Operations Specialist</t>
+          <t>Sr Counsel</t>
         </is>
       </c>
       <c r="D733" s="3" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E733" s="3" t="inlineStr">
@@ -27582,12 +27582,12 @@
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G733" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/16638</t>
+          <t>https://careers.aramco.com/expat_uk/job/Sr-Counsel/857034923/</t>
         </is>
       </c>
     </row>
@@ -27604,12 +27604,12 @@
       </c>
       <c r="C734" s="2" t="inlineStr">
         <is>
-          <t>Diesel Hydrotreater Specialist - Refinery Experience Only</t>
+          <t>Exploration Geoscientist</t>
         </is>
       </c>
       <c r="D734" s="2" t="inlineStr">
         <is>
-          <t>Operations Engineering Solutions Dept</t>
+          <t>Geoscience &amp; Reservoir</t>
         </is>
       </c>
       <c r="E734" s="2" t="inlineStr">
@@ -27619,214 +27619,214 @@
       </c>
       <c r="F734" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G734" s="2" t="inlineStr">
         <is>
-          <t>https://careers.aramco.com/job/17351</t>
+          <t>https://careers.aramco.com/expat_uk/job/Exploration-Geoscientist/857034723/</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" s="3" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B735" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C735" s="3" t="inlineStr">
         <is>
-          <t>Lead Electrical &amp; Subsea Power Eng.</t>
+          <t>Contracts Advisor</t>
         </is>
       </c>
       <c r="D735" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Contracts &amp; Procurement</t>
         </is>
       </c>
       <c r="E735" s="3" t="inlineStr">
         <is>
-          <t>Cairo - New Maadi, Egypt</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F735" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G735" s="3" t="inlineStr">
         <is>
-          <t>https://shell.wd3.myworkdayjobs.com/shellcareers/job/Cairo---New-Maadi/R198412</t>
+          <t>https://careers.aramco.com/expat_uk/job/Contracts-Advisor/857081023/</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B736" s="2" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C736" s="2" t="inlineStr">
         <is>
-          <t>Shell Graduate Programme 2026 - Qatar</t>
+          <t>Delayed Coker Visbreaker Specialist  - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D736" s="2" t="inlineStr">
         <is>
-          <t>Graduate Programme</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E736" s="2" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F736" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G736" s="2" t="inlineStr">
         <is>
-          <t>https://shell.wd3.myworkdayjobs.com/shellcareers/job/Qatar/R182165</t>
+          <t>https://careers.aramco.com/expat_uk/job/Delayed-Coker-Visbreaker-Specialist-Refinery-Experience-Only/857081923/</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" s="3" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B737" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C737" s="3" t="inlineStr">
         <is>
-          <t>Junior Lawyer (Qatari National Only)</t>
+          <t>Technology Consultant - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D737" s="3" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Business &amp; Operations</t>
         </is>
       </c>
       <c r="E737" s="3" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G737" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41638%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Technology-Consultant-Refinery-Experience-Only/857080623/</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B738" s="2" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C738" s="2" t="inlineStr">
         <is>
-          <t>Assistant Manager - Corporate Governance</t>
+          <t>Process Engineer - Utilities &amp; Tank Farm - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D738" s="2" t="inlineStr">
         <is>
-          <t>Corporate Governance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E738" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F738" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G738" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Engineer-Utilities-&amp;-Tank-Farm-Refinery-Experience-Only/857081423/</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" s="3" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B739" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C739" s="3" t="inlineStr">
         <is>
-          <t>Production Technician - Blending /Bulk</t>
+          <t>Process Engineer - Sulfur Recovery - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D739" s="3" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E739" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F739" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G739" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Process-Engineer-Sulfur-Recovery-Refinery-Experience-Only/857081623/</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B740" s="2" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C740" s="2" t="inlineStr">
         <is>
-          <t>Assistant Manager - Field Engineer &amp; Technical Services</t>
+          <t>Analyzer Engineer - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D740" s="2" t="inlineStr">
@@ -27836,209 +27836,209 @@
       </c>
       <c r="E740" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F740" s="2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G740" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Analyzer-Engineer-Refinery-Experience-Only/857082223/</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" s="3" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B741" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C741" s="3" t="inlineStr">
         <is>
-          <t>Intern - Procurement</t>
+          <t>Instrumentation Engineer - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D741" s="3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E741" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F741" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G741" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Instrumentation-Engineer-Refinery-Experience-Only/857080723/</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B742" s="2" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C742" s="2" t="inlineStr">
         <is>
-          <t>Logistics Coordinator</t>
+          <t>Maintenance Engineering Specialist - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D742" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E742" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F742" s="2" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G742" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Maintenance-Engineering-Specialist-Refinery-Experience-Only/857081323/</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" s="3" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B743" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C743" s="3" t="inlineStr">
         <is>
-          <t>Senior Officer, Contracts &amp; Procurement</t>
+          <t>Lead Turnaround Engineer - Refinery Experience Only</t>
         </is>
       </c>
       <c r="D743" s="3" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E743" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="F743" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G743" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://careers.aramco.com/expat_uk/job/Lead-Turnaround-Engineer-Refinery-Experience-Only/857080923/</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B744" s="2" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="C744" s="2" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Lead Electrical &amp; Subsea Power Eng.</t>
         </is>
       </c>
       <c r="D744" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="E744" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Cairo - New Maadi, Egypt</t>
         </is>
       </c>
       <c r="F744" s="2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G744" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://shell.wd3.myworkdayjobs.com/shellcareers/job/Cairo---New-Maadi/R198412</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="3" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B745" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="C745" s="3" t="inlineStr">
         <is>
-          <t>VP Onshore Architect</t>
+          <t>Shell Graduate Programme 2026 - Qatar</t>
         </is>
       </c>
       <c r="D745" s="3" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Graduate Programme</t>
         </is>
       </c>
       <c r="E745" s="3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F745" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G745" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://shell.wd3.myworkdayjobs.com/shellcareers/job/Qatar/R182165</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="2" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B746" s="2" t="inlineStr">
@@ -28048,34 +28048,34 @@
       </c>
       <c r="C746" s="2" t="inlineStr">
         <is>
-          <t>LENDERS E&amp;S COMPLIANCE LEADER</t>
+          <t>Junior Lawyer (Qatari National Only)</t>
         </is>
       </c>
       <c r="D746" s="2" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="E746" s="2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="F746" s="2" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="G746" s="2" t="inlineStr">
         <is>
-          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41638%5D</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="B747" s="3" t="inlineStr">
@@ -28085,32 +28085,365 @@
       </c>
       <c r="C747" s="3" t="inlineStr">
         <is>
+          <t>Assistant Manager - Corporate Governance</t>
+        </is>
+      </c>
+      <c r="D747" s="3" t="inlineStr">
+        <is>
+          <t>Corporate Governance</t>
+        </is>
+      </c>
+      <c r="E747" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F747" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G747" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C748" s="2" t="inlineStr">
+        <is>
+          <t>Production Technician - Blending /Bulk</t>
+        </is>
+      </c>
+      <c r="D748" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="E748" s="2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F748" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G748" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="3" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B749" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C749" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Manager - Field Engineer &amp; Technical Services</t>
+        </is>
+      </c>
+      <c r="D749" s="3" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E749" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F749" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="G749" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C750" s="2" t="inlineStr">
+        <is>
+          <t>Intern - Procurement</t>
+        </is>
+      </c>
+      <c r="D750" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E750" s="2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F750" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G750" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="3" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B751" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C751" s="3" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="D751" s="3" t="inlineStr">
+        <is>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="E751" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F751" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G751" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C752" s="2" t="inlineStr">
+        <is>
+          <t>Senior Officer, Contracts &amp; Procurement</t>
+        </is>
+      </c>
+      <c r="D752" s="2" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E752" s="2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F752" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="3" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B753" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C753" s="3" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="D753" s="3" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E753" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F753" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="G753" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C754" s="2" t="inlineStr">
+        <is>
+          <t>VP Onshore Architect</t>
+        </is>
+      </c>
+      <c r="D754" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="E754" s="2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F754" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="G754" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="3" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B755" s="3" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C755" s="3" t="inlineStr">
+        <is>
+          <t>LENDERS E&amp;S COMPLIANCE LEADER</t>
+        </is>
+      </c>
+      <c r="D755" s="3" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="E755" s="3" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F755" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="G755" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41568%5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="C756" s="2" t="inlineStr">
+        <is>
           <t>Production Engineer</t>
         </is>
       </c>
-      <c r="D747" s="3" t="inlineStr">
+      <c r="D756" s="2" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="E747" s="3" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="F747" s="3" t="inlineStr">
+      <c r="E756" s="2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="F756" s="2" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="G747" s="3" t="inlineStr">
+      <c r="G756" s="2" t="inlineStr">
         <is>
           <t>https://jobs.totalenergies.com/en_US/careers/SearchJobs/?3834=%5B41652%5D</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G747"/>
+  <autoFilter ref="A1:G756"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28157,7 +28490,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4">
@@ -28407,7 +28740,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
